--- a/create_forecast_basic/future/מיקום מקורי של הקבצים.xlsx
+++ b/create_forecast_basic/future/מיקום מקורי של הקבצים.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="116">
   <si>
     <t>שם קובץ</t>
   </si>
@@ -1155,6 +1155,12 @@
   <si>
     <t>work_factor_230719</t>
   </si>
+  <si>
+    <t>join_forecast_iplan_230711.ipynb</t>
+  </si>
+  <si>
+    <t>W:\Projects\הסעת המונים\01_שלב ה\קבצי עבודה\תחזיות_דמוגרפיות\תחזיות_2050\iplan\join_forecast</t>
+  </si>
 </sst>
 </file>
 
@@ -1193,7 +1199,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1214,10 +1220,6 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -4564,13 +4566,13 @@
       <c r="Z94" s="2"/>
     </row>
     <row r="95" ht="14.25" customHeight="1">
-      <c r="A95" s="6" t="s">
+      <c r="A95" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B95" s="7" t="s">
+      <c r="B95" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C95" s="6" t="s">
+      <c r="C95" s="2" t="s">
         <v>109</v>
       </c>
       <c r="D95" s="2"/>
@@ -4598,13 +4600,13 @@
       <c r="Z95" s="2"/>
     </row>
     <row r="96" ht="14.25" customHeight="1">
-      <c r="A96" s="6" t="s">
+      <c r="A96" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B96" s="7" t="s">
+      <c r="B96" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C96" s="6" t="s">
+      <c r="C96" s="2" t="s">
         <v>109</v>
       </c>
       <c r="D96" s="2"/>
@@ -4632,13 +4634,13 @@
       <c r="Z96" s="2"/>
     </row>
     <row r="97" ht="14.25" customHeight="1">
-      <c r="A97" s="6" t="s">
+      <c r="A97" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B97" s="7" t="s">
+      <c r="B97" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C97" s="6" t="s">
+      <c r="C97" s="2" t="s">
         <v>109</v>
       </c>
       <c r="D97" s="2"/>
@@ -4666,13 +4668,13 @@
       <c r="Z97" s="2"/>
     </row>
     <row r="98" ht="14.25" customHeight="1">
-      <c r="A98" s="6" t="s">
+      <c r="A98" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B98" s="7" t="s">
+      <c r="B98" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C98" s="6" t="s">
+      <c r="C98" s="2" t="s">
         <v>109</v>
       </c>
       <c r="D98" s="2"/>
@@ -4700,13 +4702,13 @@
       <c r="Z98" s="2"/>
     </row>
     <row r="99" ht="14.25" customHeight="1">
-      <c r="A99" s="6" t="s">
+      <c r="A99" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B99" s="7" t="s">
+      <c r="B99" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C99" s="6" t="s">
+      <c r="C99" s="2" t="s">
         <v>109</v>
       </c>
       <c r="D99" s="2"/>
@@ -4734,13 +4736,13 @@
       <c r="Z99" s="2"/>
     </row>
     <row r="100" ht="14.25" customHeight="1">
-      <c r="A100" s="6" t="s">
+      <c r="A100" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B100" s="7" t="s">
+      <c r="B100" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C100" s="6" t="s">
+      <c r="C100" s="2" t="s">
         <v>109</v>
       </c>
       <c r="D100" s="2"/>
@@ -4768,13 +4770,15 @@
       <c r="Z100" s="2"/>
     </row>
     <row r="101" ht="14.25" customHeight="1">
-      <c r="A101" s="6" t="s">
+      <c r="A101" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B101" s="6" t="s">
+      <c r="B101" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C101" s="8"/>
+      <c r="C101" s="2" t="s">
+        <v>109</v>
+      </c>
       <c r="D101" s="2"/>
       <c r="E101" s="2"/>
       <c r="F101" s="2"/>
@@ -4800,13 +4804,15 @@
       <c r="Z101" s="2"/>
     </row>
     <row r="102" ht="14.25" customHeight="1">
-      <c r="A102" s="6" t="s">
+      <c r="A102" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B102" s="7" t="s">
+      <c r="B102" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C102" s="8"/>
+      <c r="C102" s="2" t="s">
+        <v>109</v>
+      </c>
       <c r="D102" s="2"/>
       <c r="E102" s="2"/>
       <c r="F102" s="2"/>
@@ -4832,13 +4838,15 @@
       <c r="Z102" s="2"/>
     </row>
     <row r="103" ht="14.25" customHeight="1">
-      <c r="A103" s="6" t="s">
+      <c r="A103" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B103" s="7" t="s">
+      <c r="B103" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C103" s="8"/>
+      <c r="C103" s="2" t="s">
+        <v>109</v>
+      </c>
       <c r="D103" s="2"/>
       <c r="E103" s="2"/>
       <c r="F103" s="2"/>
@@ -4864,13 +4872,15 @@
       <c r="Z103" s="2"/>
     </row>
     <row r="104" ht="14.25" customHeight="1">
-      <c r="A104" s="6" t="s">
+      <c r="A104" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B104" s="6" t="s">
+      <c r="B104" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C104" s="8"/>
+      <c r="C104" s="2" t="s">
+        <v>109</v>
+      </c>
       <c r="D104" s="2"/>
       <c r="E104" s="2"/>
       <c r="F104" s="2"/>
@@ -4896,13 +4906,15 @@
       <c r="Z104" s="2"/>
     </row>
     <row r="105" ht="14.25" customHeight="1">
-      <c r="A105" s="6" t="s">
+      <c r="A105" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="B105" s="7" t="s">
+      <c r="B105" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C105" s="8"/>
+      <c r="C105" s="2" t="s">
+        <v>109</v>
+      </c>
       <c r="D105" s="2"/>
       <c r="E105" s="2"/>
       <c r="F105" s="2"/>
@@ -4928,9 +4940,9 @@
       <c r="Z105" s="2"/>
     </row>
     <row r="106" ht="14.25" customHeight="1">
-      <c r="A106" s="6"/>
-      <c r="B106" s="7"/>
-      <c r="C106" s="8"/>
+      <c r="A106" s="2"/>
+      <c r="B106" s="2"/>
+      <c r="C106" s="2"/>
       <c r="D106" s="2"/>
       <c r="E106" s="2"/>
       <c r="F106" s="2"/>
@@ -4956,9 +4968,15 @@
       <c r="Z106" s="2"/>
     </row>
     <row r="107" ht="14.25" customHeight="1">
-      <c r="A107" s="2"/>
-      <c r="B107" s="9"/>
-      <c r="C107" s="2"/>
+      <c r="A107" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B107" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>114</v>
+      </c>
       <c r="D107" s="2"/>
       <c r="E107" s="2"/>
       <c r="F107" s="2"/>
@@ -4984,9 +5002,15 @@
       <c r="Z107" s="2"/>
     </row>
     <row r="108" ht="14.25" customHeight="1">
-      <c r="A108" s="2"/>
-      <c r="B108" s="2"/>
-      <c r="C108" s="2"/>
+      <c r="A108" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B108" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C108" s="6" t="s">
+        <v>114</v>
+      </c>
       <c r="D108" s="2"/>
       <c r="E108" s="2"/>
       <c r="F108" s="2"/>
@@ -5012,9 +5036,15 @@
       <c r="Z108" s="2"/>
     </row>
     <row r="109" ht="14.25" customHeight="1">
-      <c r="A109" s="2"/>
-      <c r="B109" s="2"/>
-      <c r="C109" s="2"/>
+      <c r="A109" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B109" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C109" s="6" t="s">
+        <v>114</v>
+      </c>
       <c r="D109" s="2"/>
       <c r="E109" s="2"/>
       <c r="F109" s="2"/>
@@ -5040,9 +5070,15 @@
       <c r="Z109" s="2"/>
     </row>
     <row r="110" ht="14.25" customHeight="1">
-      <c r="A110" s="2"/>
-      <c r="B110" s="2"/>
-      <c r="C110" s="2"/>
+      <c r="A110" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B110" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C110" s="6" t="s">
+        <v>114</v>
+      </c>
       <c r="D110" s="2"/>
       <c r="E110" s="2"/>
       <c r="F110" s="2"/>
@@ -5068,9 +5104,15 @@
       <c r="Z110" s="2"/>
     </row>
     <row r="111" ht="14.25" customHeight="1">
-      <c r="A111" s="2"/>
-      <c r="B111" s="2"/>
-      <c r="C111" s="2"/>
+      <c r="A111" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B111" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C111" s="6" t="s">
+        <v>114</v>
+      </c>
       <c r="D111" s="2"/>
       <c r="E111" s="2"/>
       <c r="F111" s="2"/>
@@ -5096,9 +5138,15 @@
       <c r="Z111" s="2"/>
     </row>
     <row r="112" ht="14.25" customHeight="1">
-      <c r="A112" s="2"/>
-      <c r="B112" s="2"/>
-      <c r="C112" s="2"/>
+      <c r="A112" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B112" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C112" s="6" t="s">
+        <v>114</v>
+      </c>
       <c r="D112" s="2"/>
       <c r="E112" s="2"/>
       <c r="F112" s="2"/>
@@ -5124,9 +5172,15 @@
       <c r="Z112" s="2"/>
     </row>
     <row r="113" ht="14.25" customHeight="1">
-      <c r="A113" s="2"/>
-      <c r="B113" s="2"/>
-      <c r="C113" s="2"/>
+      <c r="A113" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B113" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C113" s="6" t="s">
+        <v>114</v>
+      </c>
       <c r="D113" s="2"/>
       <c r="E113" s="2"/>
       <c r="F113" s="2"/>
@@ -5152,9 +5206,15 @@
       <c r="Z113" s="2"/>
     </row>
     <row r="114" ht="14.25" customHeight="1">
-      <c r="A114" s="2"/>
-      <c r="B114" s="2"/>
-      <c r="C114" s="2"/>
+      <c r="A114" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B114" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C114" s="6" t="s">
+        <v>114</v>
+      </c>
       <c r="D114" s="2"/>
       <c r="E114" s="2"/>
       <c r="F114" s="2"/>

--- a/create_forecast_basic/future/מיקום מקורי של הקבצים.xlsx
+++ b/create_forecast_basic/future/מיקום מקורי של הקבצים.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="146">
   <si>
     <t>שם קובץ</t>
   </si>
@@ -1161,6 +1161,96 @@
   <si>
     <t>W:\Projects\הסעת המונים\01_שלב ה\קבצי עבודה\תחזיות_דמוגרפיות\תחזיות_2050\iplan\join_forecast</t>
   </si>
+  <si>
+    <t>join_kibolt_2050_Jewish_bau_230712.ipynb</t>
+  </si>
+  <si>
+    <t>W:\Projects\הסעת המונים\01_שלב ה\קבצי עבודה\תחזיות_דמוגרפיות\תחזיות_2050\bau\jew_kibolet\input</t>
+  </si>
+  <si>
+    <t>create_age_distribution_bau_230721.ipynb</t>
+  </si>
+  <si>
+    <t>W:\Projects\הסעת המונים\01_שלב ה\קבצי עבודה\תחזיות_דמוגרפיות\תחזיות_2050\bau\jew_kibolet\output</t>
+  </si>
+  <si>
+    <t>230720_forecast_pop_jewish_2020_2025_bau</t>
+  </si>
+  <si>
+    <t>W:\Projects\הסעת המונים\01_שלב ה\קבצי עבודה\תחזיות_דמוגרפיות\תחזיות_2050\bau\jew_pop</t>
+  </si>
+  <si>
+    <t>230709_join_arab_jew_pop_bau.ipynb</t>
+  </si>
+  <si>
+    <t>230720_forecast_pop_jewish_2025_2030_bau</t>
+  </si>
+  <si>
+    <t>230720_forecast_pop_jewish_2030_2035_bau</t>
+  </si>
+  <si>
+    <t>230720_forecast_pop_jewish_2035_2040_bau</t>
+  </si>
+  <si>
+    <t>230720_forecast_pop_jewish_2040_2045_bau</t>
+  </si>
+  <si>
+    <t>230720_forecast_pop_jewish_2045_2050_bau</t>
+  </si>
+  <si>
+    <t>230720_pop_2025_bau</t>
+  </si>
+  <si>
+    <t>W:\Projects\הסעת המונים\01_שלב ה\קבצי עבודה\תחזיות_דמוגרפיות\תחזיות_2050\bau\join_pop</t>
+  </si>
+  <si>
+    <t>change_pop_to_bau_goals_till_2050_230711.ipynb</t>
+  </si>
+  <si>
+    <t>230720_pop_2030_bau</t>
+  </si>
+  <si>
+    <t>230720_pop_2035_bau</t>
+  </si>
+  <si>
+    <t>230720_pop_2040_bau</t>
+  </si>
+  <si>
+    <t>230720_pop_2045_bau</t>
+  </si>
+  <si>
+    <t>230720_pop_2050_bau</t>
+  </si>
+  <si>
+    <t>gov_goals_2025_BAU</t>
+  </si>
+  <si>
+    <t>gov_goals_2030_BAU</t>
+  </si>
+  <si>
+    <t>gov_goals_2035_BAU</t>
+  </si>
+  <si>
+    <t>gov_goals_2040_BAU</t>
+  </si>
+  <si>
+    <t>gov_goals_2045_BAU</t>
+  </si>
+  <si>
+    <t>gov_goals_2050_BAU</t>
+  </si>
+  <si>
+    <t>W:\Projects\הסעת המונים\01_שלב ה\קבצי עבודה\תחזיות_דמוגרפיות\תחזיות_2050\bau\change_pop</t>
+  </si>
+  <si>
+    <t>creat_forecast_2050_bau_230720.ipynb</t>
+  </si>
+  <si>
+    <t>join_forecast_bau_230711.ipynb</t>
+  </si>
+  <si>
+    <t>W:\Projects\הסעת המונים\01_שלב ה\קבצי עבודה\תחזיות_דמוגרפיות\תחזיות_2050\bau\join_forecast</t>
+  </si>
 </sst>
 </file>
 
@@ -1199,7 +1289,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1222,6 +1312,7 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -4968,13 +5059,13 @@
       <c r="Z106" s="2"/>
     </row>
     <row r="107" ht="14.25" customHeight="1">
-      <c r="A107" s="6" t="s">
+      <c r="A107" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B107" s="6" t="s">
+      <c r="B107" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C107" s="6" t="s">
+      <c r="C107" s="2" t="s">
         <v>114</v>
       </c>
       <c r="D107" s="2"/>
@@ -5002,13 +5093,13 @@
       <c r="Z107" s="2"/>
     </row>
     <row r="108" ht="14.25" customHeight="1">
-      <c r="A108" s="6" t="s">
+      <c r="A108" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B108" s="7" t="s">
+      <c r="B108" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C108" s="6" t="s">
+      <c r="C108" s="2" t="s">
         <v>114</v>
       </c>
       <c r="D108" s="2"/>
@@ -5036,13 +5127,13 @@
       <c r="Z108" s="2"/>
     </row>
     <row r="109" ht="14.25" customHeight="1">
-      <c r="A109" s="6" t="s">
+      <c r="A109" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B109" s="7" t="s">
+      <c r="B109" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C109" s="6" t="s">
+      <c r="C109" s="2" t="s">
         <v>114</v>
       </c>
       <c r="D109" s="2"/>
@@ -5070,13 +5161,13 @@
       <c r="Z109" s="2"/>
     </row>
     <row r="110" ht="14.25" customHeight="1">
-      <c r="A110" s="6" t="s">
+      <c r="A110" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B110" s="7" t="s">
+      <c r="B110" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C110" s="6" t="s">
+      <c r="C110" s="2" t="s">
         <v>114</v>
       </c>
       <c r="D110" s="2"/>
@@ -5104,13 +5195,13 @@
       <c r="Z110" s="2"/>
     </row>
     <row r="111" ht="14.25" customHeight="1">
-      <c r="A111" s="6" t="s">
+      <c r="A111" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B111" s="7" t="s">
+      <c r="B111" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C111" s="6" t="s">
+      <c r="C111" s="2" t="s">
         <v>114</v>
       </c>
       <c r="D111" s="2"/>
@@ -5138,13 +5229,13 @@
       <c r="Z111" s="2"/>
     </row>
     <row r="112" ht="14.25" customHeight="1">
-      <c r="A112" s="6" t="s">
+      <c r="A112" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B112" s="7" t="s">
+      <c r="B112" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C112" s="6" t="s">
+      <c r="C112" s="2" t="s">
         <v>114</v>
       </c>
       <c r="D112" s="2"/>
@@ -5172,13 +5263,13 @@
       <c r="Z112" s="2"/>
     </row>
     <row r="113" ht="14.25" customHeight="1">
-      <c r="A113" s="6" t="s">
+      <c r="A113" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B113" s="7" t="s">
+      <c r="B113" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C113" s="6" t="s">
+      <c r="C113" s="2" t="s">
         <v>114</v>
       </c>
       <c r="D113" s="2"/>
@@ -5206,13 +5297,13 @@
       <c r="Z113" s="2"/>
     </row>
     <row r="114" ht="14.25" customHeight="1">
-      <c r="A114" s="6" t="s">
+      <c r="A114" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B114" s="7" t="s">
+      <c r="B114" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C114" s="6" t="s">
+      <c r="C114" s="2" t="s">
         <v>114</v>
       </c>
       <c r="D114" s="2"/>
@@ -5268,9 +5359,15 @@
       <c r="Z115" s="2"/>
     </row>
     <row r="116" ht="14.25" customHeight="1">
-      <c r="A116" s="2"/>
-      <c r="B116" s="2"/>
-      <c r="C116" s="2"/>
+      <c r="A116" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B116" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C116" s="6" t="s">
+        <v>116</v>
+      </c>
       <c r="D116" s="2"/>
       <c r="E116" s="2"/>
       <c r="F116" s="2"/>
@@ -5296,9 +5393,15 @@
       <c r="Z116" s="2"/>
     </row>
     <row r="117" ht="14.25" customHeight="1">
-      <c r="A117" s="2"/>
-      <c r="B117" s="2"/>
-      <c r="C117" s="2"/>
+      <c r="A117" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B117" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C117" s="6" t="s">
+        <v>116</v>
+      </c>
       <c r="D117" s="2"/>
       <c r="E117" s="2"/>
       <c r="F117" s="2"/>
@@ -5324,9 +5427,15 @@
       <c r="Z117" s="2"/>
     </row>
     <row r="118" ht="14.25" customHeight="1">
-      <c r="A118" s="2"/>
-      <c r="B118" s="2"/>
-      <c r="C118" s="2"/>
+      <c r="A118" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B118" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C118" s="6" t="s">
+        <v>116</v>
+      </c>
       <c r="D118" s="2"/>
       <c r="E118" s="2"/>
       <c r="F118" s="2"/>
@@ -5352,9 +5461,15 @@
       <c r="Z118" s="2"/>
     </row>
     <row r="119" ht="14.25" customHeight="1">
-      <c r="A119" s="2"/>
-      <c r="B119" s="2"/>
-      <c r="C119" s="2"/>
+      <c r="A119" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B119" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C119" s="6" t="s">
+        <v>116</v>
+      </c>
       <c r="D119" s="2"/>
       <c r="E119" s="2"/>
       <c r="F119" s="2"/>
@@ -5380,9 +5495,15 @@
       <c r="Z119" s="2"/>
     </row>
     <row r="120" ht="14.25" customHeight="1">
-      <c r="A120" s="2"/>
-      <c r="B120" s="2"/>
-      <c r="C120" s="2"/>
+      <c r="A120" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B120" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C120" s="6" t="s">
+        <v>116</v>
+      </c>
       <c r="D120" s="2"/>
       <c r="E120" s="2"/>
       <c r="F120" s="2"/>
@@ -5408,9 +5529,15 @@
       <c r="Z120" s="2"/>
     </row>
     <row r="121" ht="14.25" customHeight="1">
-      <c r="A121" s="2"/>
-      <c r="B121" s="2"/>
-      <c r="C121" s="2"/>
+      <c r="A121" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B121" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C121" s="6" t="s">
+        <v>116</v>
+      </c>
       <c r="D121" s="2"/>
       <c r="E121" s="2"/>
       <c r="F121" s="2"/>
@@ -5464,9 +5591,15 @@
       <c r="Z122" s="2"/>
     </row>
     <row r="123" ht="14.25" customHeight="1">
-      <c r="A123" s="2"/>
-      <c r="B123" s="2"/>
-      <c r="C123" s="2"/>
+      <c r="A123" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B123" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C123" s="6" t="s">
+        <v>118</v>
+      </c>
       <c r="D123" s="2"/>
       <c r="E123" s="2"/>
       <c r="F123" s="2"/>
@@ -5492,9 +5625,15 @@
       <c r="Z123" s="2"/>
     </row>
     <row r="124" ht="14.25" customHeight="1">
-      <c r="A124" s="2"/>
-      <c r="B124" s="2"/>
-      <c r="C124" s="2"/>
+      <c r="A124" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B124" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C124" s="6" t="s">
+        <v>118</v>
+      </c>
       <c r="D124" s="2"/>
       <c r="E124" s="2"/>
       <c r="F124" s="2"/>
@@ -5520,9 +5659,15 @@
       <c r="Z124" s="2"/>
     </row>
     <row r="125" ht="14.25" customHeight="1">
-      <c r="A125" s="2"/>
-      <c r="B125" s="2"/>
-      <c r="C125" s="2"/>
+      <c r="A125" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B125" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C125" s="6" t="s">
+        <v>118</v>
+      </c>
       <c r="D125" s="2"/>
       <c r="E125" s="2"/>
       <c r="F125" s="2"/>
@@ -5548,9 +5693,15 @@
       <c r="Z125" s="2"/>
     </row>
     <row r="126" ht="14.25" customHeight="1">
-      <c r="A126" s="2"/>
-      <c r="B126" s="2"/>
-      <c r="C126" s="2"/>
+      <c r="A126" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B126" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C126" s="6" t="s">
+        <v>118</v>
+      </c>
       <c r="D126" s="2"/>
       <c r="E126" s="2"/>
       <c r="F126" s="2"/>
@@ -5604,9 +5755,15 @@
       <c r="Z127" s="2"/>
     </row>
     <row r="128" ht="14.25" customHeight="1">
-      <c r="A128" s="2"/>
-      <c r="B128" s="2"/>
-      <c r="C128" s="2"/>
+      <c r="A128" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="B128" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="C128" s="6" t="s">
+        <v>122</v>
+      </c>
       <c r="D128" s="2"/>
       <c r="E128" s="2"/>
       <c r="F128" s="2"/>
@@ -5632,9 +5789,15 @@
       <c r="Z128" s="2"/>
     </row>
     <row r="129" ht="14.25" customHeight="1">
-      <c r="A129" s="2"/>
-      <c r="B129" s="2"/>
-      <c r="C129" s="2"/>
+      <c r="A129" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="B129" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="C129" s="6" t="s">
+        <v>122</v>
+      </c>
       <c r="D129" s="2"/>
       <c r="E129" s="2"/>
       <c r="F129" s="2"/>
@@ -5660,9 +5823,15 @@
       <c r="Z129" s="2"/>
     </row>
     <row r="130" ht="14.25" customHeight="1">
-      <c r="A130" s="2"/>
-      <c r="B130" s="2"/>
-      <c r="C130" s="2"/>
+      <c r="A130" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B130" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="C130" s="6" t="s">
+        <v>122</v>
+      </c>
       <c r="D130" s="2"/>
       <c r="E130" s="2"/>
       <c r="F130" s="2"/>
@@ -5688,9 +5857,15 @@
       <c r="Z130" s="2"/>
     </row>
     <row r="131" ht="14.25" customHeight="1">
-      <c r="A131" s="2"/>
-      <c r="B131" s="2"/>
-      <c r="C131" s="2"/>
+      <c r="A131" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="B131" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="C131" s="6" t="s">
+        <v>122</v>
+      </c>
       <c r="D131" s="2"/>
       <c r="E131" s="2"/>
       <c r="F131" s="2"/>
@@ -5716,9 +5891,15 @@
       <c r="Z131" s="2"/>
     </row>
     <row r="132" ht="14.25" customHeight="1">
-      <c r="A132" s="2"/>
-      <c r="B132" s="2"/>
-      <c r="C132" s="2"/>
+      <c r="A132" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B132" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="C132" s="6" t="s">
+        <v>122</v>
+      </c>
       <c r="D132" s="2"/>
       <c r="E132" s="2"/>
       <c r="F132" s="2"/>
@@ -5744,9 +5925,15 @@
       <c r="Z132" s="2"/>
     </row>
     <row r="133" ht="14.25" customHeight="1">
-      <c r="A133" s="2"/>
-      <c r="B133" s="2"/>
-      <c r="C133" s="2"/>
+      <c r="A133" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="B133" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="C133" s="6" t="s">
+        <v>122</v>
+      </c>
       <c r="D133" s="2"/>
       <c r="E133" s="2"/>
       <c r="F133" s="2"/>
@@ -5772,9 +5959,15 @@
       <c r="Z133" s="2"/>
     </row>
     <row r="134" ht="14.25" customHeight="1">
-      <c r="A134" s="2"/>
-      <c r="B134" s="2"/>
-      <c r="C134" s="2"/>
+      <c r="A134" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B134" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C134" s="6" t="s">
+        <v>122</v>
+      </c>
       <c r="D134" s="2"/>
       <c r="E134" s="2"/>
       <c r="F134" s="2"/>
@@ -5800,9 +5993,15 @@
       <c r="Z134" s="2"/>
     </row>
     <row r="135" ht="14.25" customHeight="1">
-      <c r="A135" s="2"/>
-      <c r="B135" s="2"/>
-      <c r="C135" s="2"/>
+      <c r="A135" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B135" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C135" s="6" t="s">
+        <v>122</v>
+      </c>
       <c r="D135" s="2"/>
       <c r="E135" s="2"/>
       <c r="F135" s="2"/>
@@ -5828,9 +6027,15 @@
       <c r="Z135" s="2"/>
     </row>
     <row r="136" ht="14.25" customHeight="1">
-      <c r="A136" s="2"/>
-      <c r="B136" s="2"/>
-      <c r="C136" s="2"/>
+      <c r="A136" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B136" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C136" s="6" t="s">
+        <v>122</v>
+      </c>
       <c r="D136" s="2"/>
       <c r="E136" s="2"/>
       <c r="F136" s="2"/>
@@ -5856,9 +6061,15 @@
       <c r="Z136" s="2"/>
     </row>
     <row r="137" ht="14.25" customHeight="1">
-      <c r="A137" s="2"/>
-      <c r="B137" s="2"/>
-      <c r="C137" s="2"/>
+      <c r="A137" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B137" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C137" s="6" t="s">
+        <v>122</v>
+      </c>
       <c r="D137" s="2"/>
       <c r="E137" s="2"/>
       <c r="F137" s="2"/>
@@ -5884,9 +6095,15 @@
       <c r="Z137" s="2"/>
     </row>
     <row r="138" ht="14.25" customHeight="1">
-      <c r="A138" s="2"/>
-      <c r="B138" s="2"/>
-      <c r="C138" s="2"/>
+      <c r="A138" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B138" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C138" s="6" t="s">
+        <v>122</v>
+      </c>
       <c r="D138" s="2"/>
       <c r="E138" s="2"/>
       <c r="F138" s="2"/>
@@ -5912,9 +6129,15 @@
       <c r="Z138" s="2"/>
     </row>
     <row r="139" ht="14.25" customHeight="1">
-      <c r="A139" s="2"/>
-      <c r="B139" s="2"/>
-      <c r="C139" s="2"/>
+      <c r="A139" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B139" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C139" s="6" t="s">
+        <v>122</v>
+      </c>
       <c r="D139" s="2"/>
       <c r="E139" s="2"/>
       <c r="F139" s="2"/>
@@ -5968,9 +6191,15 @@
       <c r="Z140" s="2"/>
     </row>
     <row r="141" ht="14.25" customHeight="1">
-      <c r="A141" s="2"/>
-      <c r="B141" s="2"/>
-      <c r="C141" s="2"/>
+      <c r="A141" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B141" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="C141" s="6" t="s">
+        <v>130</v>
+      </c>
       <c r="D141" s="2"/>
       <c r="E141" s="2"/>
       <c r="F141" s="2"/>
@@ -5996,9 +6225,15 @@
       <c r="Z141" s="2"/>
     </row>
     <row r="142" ht="14.25" customHeight="1">
-      <c r="A142" s="2"/>
-      <c r="B142" s="2"/>
-      <c r="C142" s="2"/>
+      <c r="A142" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B142" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="C142" s="6" t="s">
+        <v>130</v>
+      </c>
       <c r="D142" s="2"/>
       <c r="E142" s="2"/>
       <c r="F142" s="2"/>
@@ -6024,9 +6259,15 @@
       <c r="Z142" s="2"/>
     </row>
     <row r="143" ht="14.25" customHeight="1">
-      <c r="A143" s="2"/>
-      <c r="B143" s="2"/>
-      <c r="C143" s="2"/>
+      <c r="A143" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="B143" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="C143" s="6" t="s">
+        <v>130</v>
+      </c>
       <c r="D143" s="2"/>
       <c r="E143" s="2"/>
       <c r="F143" s="2"/>
@@ -6052,9 +6293,15 @@
       <c r="Z143" s="2"/>
     </row>
     <row r="144" ht="14.25" customHeight="1">
-      <c r="A144" s="2"/>
-      <c r="B144" s="2"/>
-      <c r="C144" s="2"/>
+      <c r="A144" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="B144" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="C144" s="6" t="s">
+        <v>130</v>
+      </c>
       <c r="D144" s="2"/>
       <c r="E144" s="2"/>
       <c r="F144" s="2"/>
@@ -6080,9 +6327,15 @@
       <c r="Z144" s="2"/>
     </row>
     <row r="145" ht="14.25" customHeight="1">
-      <c r="A145" s="2"/>
-      <c r="B145" s="2"/>
-      <c r="C145" s="2"/>
+      <c r="A145" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B145" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="C145" s="6" t="s">
+        <v>130</v>
+      </c>
       <c r="D145" s="2"/>
       <c r="E145" s="2"/>
       <c r="F145" s="2"/>
@@ -6108,9 +6361,15 @@
       <c r="Z145" s="2"/>
     </row>
     <row r="146" ht="14.25" customHeight="1">
-      <c r="A146" s="2"/>
-      <c r="B146" s="2"/>
-      <c r="C146" s="2"/>
+      <c r="A146" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B146" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="C146" s="6" t="s">
+        <v>130</v>
+      </c>
       <c r="D146" s="2"/>
       <c r="E146" s="2"/>
       <c r="F146" s="2"/>
@@ -6136,9 +6395,15 @@
       <c r="Z146" s="2"/>
     </row>
     <row r="147" ht="14.25" customHeight="1">
-      <c r="A147" s="2"/>
-      <c r="B147" s="2"/>
-      <c r="C147" s="2"/>
+      <c r="A147" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="B147" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C147" s="6" t="s">
+        <v>130</v>
+      </c>
       <c r="D147" s="2"/>
       <c r="E147" s="2"/>
       <c r="F147" s="2"/>
@@ -6164,9 +6429,15 @@
       <c r="Z147" s="2"/>
     </row>
     <row r="148" ht="14.25" customHeight="1">
-      <c r="A148" s="2"/>
-      <c r="B148" s="2"/>
-      <c r="C148" s="2"/>
+      <c r="A148" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="B148" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C148" s="6" t="s">
+        <v>130</v>
+      </c>
       <c r="D148" s="2"/>
       <c r="E148" s="2"/>
       <c r="F148" s="2"/>
@@ -6192,9 +6463,15 @@
       <c r="Z148" s="2"/>
     </row>
     <row r="149" ht="14.25" customHeight="1">
-      <c r="A149" s="2"/>
-      <c r="B149" s="2"/>
-      <c r="C149" s="2"/>
+      <c r="A149" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B149" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C149" s="6" t="s">
+        <v>130</v>
+      </c>
       <c r="D149" s="2"/>
       <c r="E149" s="2"/>
       <c r="F149" s="2"/>
@@ -6220,9 +6497,15 @@
       <c r="Z149" s="2"/>
     </row>
     <row r="150" ht="14.25" customHeight="1">
-      <c r="A150" s="2"/>
-      <c r="B150" s="2"/>
-      <c r="C150" s="2"/>
+      <c r="A150" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="B150" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C150" s="6" t="s">
+        <v>130</v>
+      </c>
       <c r="D150" s="2"/>
       <c r="E150" s="2"/>
       <c r="F150" s="2"/>
@@ -6248,9 +6531,15 @@
       <c r="Z150" s="2"/>
     </row>
     <row r="151" ht="14.25" customHeight="1">
-      <c r="A151" s="2"/>
-      <c r="B151" s="2"/>
-      <c r="C151" s="2"/>
+      <c r="A151" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="B151" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C151" s="6" t="s">
+        <v>130</v>
+      </c>
       <c r="D151" s="2"/>
       <c r="E151" s="2"/>
       <c r="F151" s="2"/>
@@ -6276,9 +6565,15 @@
       <c r="Z151" s="2"/>
     </row>
     <row r="152" ht="14.25" customHeight="1">
-      <c r="A152" s="2"/>
-      <c r="B152" s="2"/>
-      <c r="C152" s="2"/>
+      <c r="A152" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="B152" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C152" s="6" t="s">
+        <v>130</v>
+      </c>
       <c r="D152" s="2"/>
       <c r="E152" s="2"/>
       <c r="F152" s="2"/>
@@ -6304,9 +6599,15 @@
       <c r="Z152" s="2"/>
     </row>
     <row r="153" ht="14.25" customHeight="1">
-      <c r="A153" s="2"/>
-      <c r="B153" s="2"/>
-      <c r="C153" s="2"/>
+      <c r="A153" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B153" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C153" s="6" t="s">
+        <v>130</v>
+      </c>
       <c r="D153" s="2"/>
       <c r="E153" s="2"/>
       <c r="F153" s="2"/>
@@ -6360,9 +6661,15 @@
       <c r="Z154" s="2"/>
     </row>
     <row r="155" ht="14.25" customHeight="1">
-      <c r="A155" s="2"/>
-      <c r="B155" s="2"/>
-      <c r="C155" s="2"/>
+      <c r="A155" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B155" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="C155" s="6" t="s">
+        <v>143</v>
+      </c>
       <c r="D155" s="2"/>
       <c r="E155" s="2"/>
       <c r="F155" s="2"/>
@@ -6388,9 +6695,15 @@
       <c r="Z155" s="2"/>
     </row>
     <row r="156" ht="14.25" customHeight="1">
-      <c r="A156" s="2"/>
-      <c r="B156" s="2"/>
-      <c r="C156" s="2"/>
+      <c r="A156" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B156" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="C156" s="6" t="s">
+        <v>143</v>
+      </c>
       <c r="D156" s="2"/>
       <c r="E156" s="2"/>
       <c r="F156" s="2"/>
@@ -6416,9 +6729,15 @@
       <c r="Z156" s="2"/>
     </row>
     <row r="157" ht="14.25" customHeight="1">
-      <c r="A157" s="2"/>
-      <c r="B157" s="2"/>
-      <c r="C157" s="2"/>
+      <c r="A157" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="B157" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="C157" s="6" t="s">
+        <v>143</v>
+      </c>
       <c r="D157" s="2"/>
       <c r="E157" s="2"/>
       <c r="F157" s="2"/>
@@ -6444,9 +6763,15 @@
       <c r="Z157" s="2"/>
     </row>
     <row r="158" ht="14.25" customHeight="1">
-      <c r="A158" s="2"/>
-      <c r="B158" s="2"/>
-      <c r="C158" s="2"/>
+      <c r="A158" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="B158" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="C158" s="6" t="s">
+        <v>143</v>
+      </c>
       <c r="D158" s="2"/>
       <c r="E158" s="2"/>
       <c r="F158" s="2"/>
@@ -6472,9 +6797,15 @@
       <c r="Z158" s="2"/>
     </row>
     <row r="159" ht="14.25" customHeight="1">
-      <c r="A159" s="2"/>
-      <c r="B159" s="2"/>
-      <c r="C159" s="2"/>
+      <c r="A159" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B159" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="C159" s="6" t="s">
+        <v>143</v>
+      </c>
       <c r="D159" s="2"/>
       <c r="E159" s="2"/>
       <c r="F159" s="2"/>
@@ -6500,9 +6831,15 @@
       <c r="Z159" s="2"/>
     </row>
     <row r="160" ht="14.25" customHeight="1">
-      <c r="A160" s="2"/>
-      <c r="B160" s="2"/>
-      <c r="C160" s="2"/>
+      <c r="A160" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B160" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="C160" s="6" t="s">
+        <v>143</v>
+      </c>
       <c r="D160" s="2"/>
       <c r="E160" s="2"/>
       <c r="F160" s="2"/>
@@ -6528,9 +6865,15 @@
       <c r="Z160" s="2"/>
     </row>
     <row r="161" ht="14.25" customHeight="1">
-      <c r="A161" s="2"/>
-      <c r="B161" s="2"/>
-      <c r="C161" s="2"/>
+      <c r="A161" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B161" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C161" s="6" t="s">
+        <v>143</v>
+      </c>
       <c r="D161" s="2"/>
       <c r="E161" s="2"/>
       <c r="F161" s="2"/>
@@ -6556,9 +6899,15 @@
       <c r="Z161" s="2"/>
     </row>
     <row r="162" ht="14.25" customHeight="1">
-      <c r="A162" s="2"/>
-      <c r="B162" s="2"/>
-      <c r="C162" s="2"/>
+      <c r="A162" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B162" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C162" s="6" t="s">
+        <v>143</v>
+      </c>
       <c r="D162" s="2"/>
       <c r="E162" s="2"/>
       <c r="F162" s="2"/>
@@ -6584,9 +6933,15 @@
       <c r="Z162" s="2"/>
     </row>
     <row r="163" ht="14.25" customHeight="1">
-      <c r="A163" s="2"/>
-      <c r="B163" s="2"/>
-      <c r="C163" s="2"/>
+      <c r="A163" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B163" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C163" s="6" t="s">
+        <v>143</v>
+      </c>
       <c r="D163" s="2"/>
       <c r="E163" s="2"/>
       <c r="F163" s="2"/>
@@ -6612,9 +6967,15 @@
       <c r="Z163" s="2"/>
     </row>
     <row r="164" ht="14.25" customHeight="1">
-      <c r="A164" s="2"/>
-      <c r="B164" s="2"/>
-      <c r="C164" s="2"/>
+      <c r="A164" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B164" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C164" s="6" t="s">
+        <v>143</v>
+      </c>
       <c r="D164" s="2"/>
       <c r="E164" s="2"/>
       <c r="F164" s="2"/>
@@ -6640,9 +7001,9 @@
       <c r="Z164" s="2"/>
     </row>
     <row r="165" ht="14.25" customHeight="1">
-      <c r="A165" s="2"/>
-      <c r="B165" s="2"/>
-      <c r="C165" s="2"/>
+      <c r="A165" s="6"/>
+      <c r="B165" s="7"/>
+      <c r="C165" s="8"/>
       <c r="D165" s="2"/>
       <c r="E165" s="2"/>
       <c r="F165" s="2"/>
@@ -6668,9 +7029,15 @@
       <c r="Z165" s="2"/>
     </row>
     <row r="166" ht="14.25" customHeight="1">
-      <c r="A166" s="2"/>
-      <c r="B166" s="2"/>
-      <c r="C166" s="2"/>
+      <c r="A166" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B166" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C166" s="6" t="s">
+        <v>144</v>
+      </c>
       <c r="D166" s="2"/>
       <c r="E166" s="2"/>
       <c r="F166" s="2"/>
@@ -6696,9 +7063,15 @@
       <c r="Z166" s="2"/>
     </row>
     <row r="167" ht="14.25" customHeight="1">
-      <c r="A167" s="2"/>
-      <c r="B167" s="2"/>
-      <c r="C167" s="2"/>
+      <c r="A167" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B167" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="C167" s="6" t="s">
+        <v>144</v>
+      </c>
       <c r="D167" s="2"/>
       <c r="E167" s="2"/>
       <c r="F167" s="2"/>
@@ -6724,9 +7097,15 @@
       <c r="Z167" s="2"/>
     </row>
     <row r="168" ht="14.25" customHeight="1">
-      <c r="A168" s="2"/>
-      <c r="B168" s="2"/>
-      <c r="C168" s="2"/>
+      <c r="A168" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B168" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="C168" s="6" t="s">
+        <v>144</v>
+      </c>
       <c r="D168" s="2"/>
       <c r="E168" s="2"/>
       <c r="F168" s="2"/>
@@ -6752,9 +7131,15 @@
       <c r="Z168" s="2"/>
     </row>
     <row r="169" ht="14.25" customHeight="1">
-      <c r="A169" s="2"/>
-      <c r="B169" s="2"/>
-      <c r="C169" s="2"/>
+      <c r="A169" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B169" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="C169" s="6" t="s">
+        <v>144</v>
+      </c>
       <c r="D169" s="2"/>
       <c r="E169" s="2"/>
       <c r="F169" s="2"/>
@@ -6780,9 +7165,15 @@
       <c r="Z169" s="2"/>
     </row>
     <row r="170" ht="14.25" customHeight="1">
-      <c r="A170" s="2"/>
-      <c r="B170" s="2"/>
-      <c r="C170" s="2"/>
+      <c r="A170" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B170" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="C170" s="6" t="s">
+        <v>144</v>
+      </c>
       <c r="D170" s="2"/>
       <c r="E170" s="2"/>
       <c r="F170" s="2"/>
@@ -6808,9 +7199,15 @@
       <c r="Z170" s="2"/>
     </row>
     <row r="171" ht="14.25" customHeight="1">
-      <c r="A171" s="2"/>
-      <c r="B171" s="2"/>
-      <c r="C171" s="2"/>
+      <c r="A171" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B171" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="C171" s="6" t="s">
+        <v>144</v>
+      </c>
       <c r="D171" s="2"/>
       <c r="E171" s="2"/>
       <c r="F171" s="2"/>
@@ -6836,9 +7233,15 @@
       <c r="Z171" s="2"/>
     </row>
     <row r="172" ht="14.25" customHeight="1">
-      <c r="A172" s="2"/>
-      <c r="B172" s="2"/>
-      <c r="C172" s="2"/>
+      <c r="A172" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B172" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="C172" s="6" t="s">
+        <v>144</v>
+      </c>
       <c r="D172" s="2"/>
       <c r="E172" s="2"/>
       <c r="F172" s="2"/>
@@ -6864,9 +7267,13 @@
       <c r="Z172" s="2"/>
     </row>
     <row r="173" ht="14.25" customHeight="1">
-      <c r="A173" s="2"/>
-      <c r="B173" s="2"/>
-      <c r="C173" s="2"/>
+      <c r="A173" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B173" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C173" s="8"/>
       <c r="D173" s="2"/>
       <c r="E173" s="2"/>
       <c r="F173" s="2"/>

--- a/create_forecast_basic/future/מיקום מקורי של הקבצים.xlsx
+++ b/create_forecast_basic/future/מיקום מקורי של הקבצים.xlsx
@@ -1,1278 +1,495 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Calc"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <extLst>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="146">
-  <si>
-    <t>שם קובץ</t>
-  </si>
-  <si>
-    <t>מיקום מקורי</t>
-  </si>
-  <si>
-    <t>קוד בשימוש</t>
-  </si>
-  <si>
-    <t>230628_Jewish_kibolt_some_towns_in_yosh_till_2050</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>W:</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>\P</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>rojects</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>\ה</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>סעת המונים\מטרו</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>\01</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>_שלב ה</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>\ק</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>בצי עבודה</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>\ת</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>חזיות_דמוגרפיות</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>\ת</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>חזיות_2050</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>\מ</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>רכיבי_תחזית</t>
-    </r>
-  </si>
-  <si>
-    <t>join_kibolt_2050_Jewish_230707.ipynb</t>
-  </si>
-  <si>
-    <t>TAZ_V4_230518_Published.shp</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>W:</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>\M</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>odel Versions</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>\4</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>.0</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>\T</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>AZ</t>
-    </r>
-  </si>
-  <si>
-    <t>kibolt_jew_by_some_taz_230628.shp</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>W:</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>\P</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>rojects</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>\ה</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>סעת המונים\מטרו</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>\01</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>_שלב ה</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>\ק</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>בצי עבודה</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>\ת</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>חזיות_דמוגרפיות</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>\ת</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>חזיות_2050</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>\מ</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>רכיבי_תחזית\SHP</t>
-    </r>
-  </si>
-  <si>
-    <t>Jewish_kibolt_some_by_plan_with_taz_num.shp</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>W:</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>\P</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>rojects</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>\ה</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>סעת המונים\מטרו</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>\01</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>_שלב ה</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>\ק</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>בצי עבודה</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>\ת</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>חזיות_דמוגרפיות</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>\ת</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>חזיות_2050</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>\מ</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>רכיבי_תחזית\SHP</t>
-    </r>
-  </si>
-  <si>
-    <t>index_for_id_polygons_230717</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>W:</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>\P</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>rojects</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>\ה</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>סעת המונים\מטרו</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>\01</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>_שלב ה</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>\ק</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>בצי עבודה</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>\ת</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>חזיות_דמוגרפיות</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>\ת</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>חזיות_2050</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>\j</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>tmt</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>\j</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>ew_kibolet</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>\i</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>nput</t>
-    </r>
-  </si>
-  <si>
-    <t>230628_id_polygons_for_index.shp</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>W:</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>\P</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>rojects</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>\ה</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>סעת המונים\מטרו</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>\01</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>_שלב ה</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>\ק</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>בצי עבודה</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>\ת</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>חזיות_דמוגרפיות</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>\ת</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>חזיות_2050</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>\מ</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>רכיבי_תחזית\SHP</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>W:</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>\P</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>rojects</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>\ה</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>סעת המונים\מטרו</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>\01</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>_שלב ה</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>\ק</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>בצי עבודה</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>\ת</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>חזיות_דמוגרפיות</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>\ת</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>חזיות_2050</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>\ה</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>תפלגות גילים\backround_files</t>
-    </r>
-  </si>
-  <si>
-    <t>create_age_distribution_230719.ipynb</t>
-  </si>
-  <si>
-    <t>forecast_2020_230720_age_dis_type</t>
-  </si>
-  <si>
-    <t>2020_jtmt_forcast_full_230720</t>
-  </si>
-  <si>
-    <t>FILE-SRV\Jtmt\projections_team\כללי\פעולות\יצירת_מצב_קיים_למס\output</t>
-  </si>
-  <si>
-    <t>230720_kibolt_jew_till_2050</t>
-  </si>
-  <si>
-    <t>W:\Projects\הסעת המונים\01_שלב ה\קבצי עבודה\תחזיות_דמוגרפיות\תחזיות_2050\jtmt\jew_kibolet\output</t>
-  </si>
-  <si>
-    <t>cost_diversity_for_age_distribution.shp</t>
-  </si>
-  <si>
-    <t>W:\Data\Forecast\creat_age_distribution\v_1\backround_files\shp</t>
-  </si>
-  <si>
-    <t>230720_forecast_pop_jewish_2020_2025_jtmt</t>
-  </si>
-  <si>
-    <t>W:\Projects\הסעת המונים\01_שלב ה\קבצי עבודה\תחזיות_דמוגרפיות\תחזיות_2050\jtmt\jew_pop</t>
-  </si>
-  <si>
-    <t>230709_join_arab_jew_pop.ipynb</t>
-  </si>
-  <si>
-    <t>230720_forecast_pop_jewish_2025_2030_jtmt</t>
-  </si>
-  <si>
-    <t>230720_forecast_pop_jewish_2030_2035_jtmt</t>
-  </si>
-  <si>
-    <t>230720_forecast_pop_jewish_2035_2040_jtmt</t>
-  </si>
-  <si>
-    <t>230720_forecast_pop_jewish_2040_2045_jtmt</t>
-  </si>
-  <si>
-    <t>230720_forecast_pop_jewish_2045_2050_jtmt</t>
-  </si>
-  <si>
-    <t>taz_Arab_Palestinian_2025</t>
-  </si>
-  <si>
-    <t>W:\Projects\הסעת המונים\01_שלב ה\קבצי עבודה\תחזיות_דמוגרפיות\תחזיות_2050\jtmt\arab_pop</t>
-  </si>
-  <si>
-    <t>taz_Arab_Palestinian_2030</t>
-  </si>
-  <si>
-    <t>taz_Arab_Palestinian_2035</t>
-  </si>
-  <si>
-    <t>taz_Arab_Palestinian_2040</t>
-  </si>
-  <si>
-    <t>taz_Arab_Palestinian_2045</t>
-  </si>
-  <si>
-    <t>taz_Arab_Palestinian_2050</t>
-  </si>
-  <si>
-    <t>join_forecast.ipynb</t>
-  </si>
-  <si>
-    <t>230720_forecast_2025_full</t>
-  </si>
-  <si>
-    <t>W:\Projects\הסעת המונים\01_שלב ה\קבצי עבודה\תחזיות_דמוגרפיות\תחזיות_2050\jtmt\join_forecast</t>
-  </si>
-  <si>
-    <t>230720_forecast_2030_full</t>
-  </si>
-  <si>
-    <t>230720_forecast_2035_full</t>
-  </si>
-  <si>
-    <t>230720_forecast_2040_full</t>
-  </si>
-  <si>
-    <t>230720_forecast_2045_full</t>
-  </si>
-  <si>
-    <t>230720_forecast_2050_full</t>
-  </si>
-  <si>
-    <t>‏‏PalestiniansResults_forecast_zone</t>
-  </si>
-  <si>
-    <t>FILE-SRV\Jtmt\projections_team\תכניות אסטרטגיות לתחבורה ירושלים\תחזיות 2050\עבודת דמוגרף\קבלת מידע\תחזיות_פלסטינים_ערבים</t>
-  </si>
-  <si>
-    <t>palestinian_from_demo_230622.ipynb</t>
-  </si>
-  <si>
-    <t>proj_zones_pls.shp</t>
-  </si>
-  <si>
-    <t>K:\projections_team\תכניות אסטרטגיות לתחבורה ירושלים\תחזיות 2050\עבודת דמוגרף\קבלת מידע\אזורי_תחזיות_פלסטינים\SHP</t>
-  </si>
-  <si>
-    <t>TAZ_V4_221212_Published.shp</t>
-  </si>
-  <si>
-    <t>W:\Model Versions\4.0\TAZ</t>
-  </si>
-  <si>
-    <t>palestinian_bld_area_pcbs_220710.shp</t>
-  </si>
-  <si>
-    <t>K:\projections_team\תכניות אסטרטגיות לתחבורה ירושלים\תחזיות 2050\עבודת דמוגרף\פיזור_אוכלוסייה_באזורי_תנועה_פלסטינאים\SHP</t>
-  </si>
-  <si>
-    <t>ezorey_tnua_600_2015_ITM.SHP</t>
-  </si>
-  <si>
-    <t>arab_growth_till_2050_from_demo_230618.ipynb</t>
-  </si>
-  <si>
-    <t>‏‏ArabTAZ_in_jeru_dis_after_jtmt</t>
-  </si>
-  <si>
-    <t>230709_arab_growth_vs_kibolt.ipynb</t>
-  </si>
-  <si>
-    <t>kibolet_with_behind_wall_230709.shp</t>
-  </si>
-  <si>
-    <t>K:\projections_team\תכניות אסטרטגיות לתחבורה ירושלים\תחזיות 2050\קיבולת_ערבי_מחוז_ירושלים</t>
-  </si>
-  <si>
-    <t>2020_jtmt_forcast_full_230710</t>
-  </si>
-  <si>
-    <t>hh_size_2050.shp</t>
-  </si>
-  <si>
-    <t>FILE-SRV\Jtmt\projections_team\תכניות אסטרטגיות לתחבורה ירושלים\תחזיות 2050\קבלת מידע\גודל משק בית\</t>
-  </si>
-  <si>
-    <t>pre_demo_growth_dislov_2025</t>
-  </si>
-  <si>
-    <t>W:\Projects\הסעת המונים\01_שלב ה\קבצי עבודה\תחזיות_דמוגרפיות\תחזיות_2050\עבודת_דמוגרף\SHP</t>
-  </si>
-  <si>
-    <t>pre_demo_growth_dislov_2030</t>
-  </si>
-  <si>
-    <t>pre_demo_growth_dislov_2035</t>
-  </si>
-  <si>
-    <t>pre_demo_growth_dislov_2040</t>
-  </si>
-  <si>
-    <t>pre_demo_growth_dislov_2045</t>
-  </si>
-  <si>
-    <t>pre_demo_growth_dislov_2050</t>
-  </si>
-  <si>
-    <t>W:\Projects\הסעת המונים\01_שלב ה\קבצי עבודה\תחזיות_דמוגרפיות\תחזיות_2050\מרכיבי_תחזית</t>
-  </si>
-  <si>
-    <t>join_kibolt_2050_Jewish_iplan_230711.ipynb</t>
-  </si>
-  <si>
-    <t>W:\Projects\הסעת המונים\01_שלב ה\קבצי עבודה\תחזיות_דמוגרפיות\תחזיות_2050\מרכיבי_תחזית\SHP</t>
-  </si>
-  <si>
-    <t>index_for_id_polygons_230712</t>
-  </si>
-  <si>
-    <t>W:\Projects\הסעת המונים\01_שלב ה\קבצי עבודה\תחזיות_דמוגרפיות\תחזיות_2050\iplan\jew_kibolet\input</t>
-  </si>
-  <si>
-    <t>230704_taz_num_convert_from_jewish_to_u_orthodox</t>
-  </si>
-  <si>
-    <t>W:\Projects\הסעת המונים\01_שלב ה\קבצי עבודה\תחזיות_דמוגרפיות\תרחישי_מלל\מרכיבי_תחזית</t>
-  </si>
-  <si>
-    <t>forecast_2020_230719_age_dis_type</t>
-  </si>
-  <si>
-    <t>W:\Projects\הסעת המונים\01_שלב ה\קבצי עבודה\תחזיות_דמוגרפיות\תחזיות_2050\התפלגות גילים\backround_files</t>
-  </si>
-  <si>
-    <t>create_age_distribution_iplan_230720.ipynb</t>
-  </si>
-  <si>
-    <t>2020_jtmt_forcast_full_230719</t>
-  </si>
-  <si>
-    <t>W:\Projects\הסעת המונים\01_שלב ה\קבצי עבודה\תחזיות_דמוגרפיות\תחזיות_2050\iplan\jew_kibolet\output</t>
-  </si>
-  <si>
-    <t>230720_forecast_pop_jewish_2020_2025_iplan</t>
-  </si>
-  <si>
-    <t>W:\Projects\הסעת המונים\01_שלב ה\קבצי עבודה\תחזיות_דמוגרפיות\תחזיות_2050\iplan\jew_pop</t>
-  </si>
-  <si>
-    <t>230709_join_arab_jew_pop_iplan.ipynb</t>
-  </si>
-  <si>
-    <t>230720_forecast_pop_jewish_2025_2030_iplan</t>
-  </si>
-  <si>
-    <t>230720_forecast_pop_jewish_2030_2035_iplan</t>
-  </si>
-  <si>
-    <t>230720_forecast_pop_jewish_2035_2040_iplan</t>
-  </si>
-  <si>
-    <t>230720_forecast_pop_jewish_2040_2045_iplan</t>
-  </si>
-  <si>
-    <t>230720_forecast_pop_jewish_2045_2050_iplan</t>
-  </si>
-  <si>
-    <t>230720_pop_2025_iplan</t>
-  </si>
-  <si>
-    <t>W:\Projects\הסעת המונים\01_שלב ה\קבצי עבודה\תחזיות_דמוגרפיות\תחזיות_2050\iplan\join_pop</t>
-  </si>
-  <si>
-    <t>change_pop_to_iplan_goals_till_2050_230711.ipynb</t>
-  </si>
-  <si>
-    <t>230720_pop_2030_iplan</t>
-  </si>
-  <si>
-    <t>230720_pop_2035_iplan</t>
-  </si>
-  <si>
-    <t>230720_pop_2040_iplan</t>
-  </si>
-  <si>
-    <t>230720_pop_2045_iplan</t>
-  </si>
-  <si>
-    <t>230720_pop_2050_iplan</t>
-  </si>
-  <si>
-    <t>gov_goals_2025_iplan</t>
-  </si>
-  <si>
-    <t>W:\Projects\הסעת המונים\01_שלב ה\קבצי עבודה\תחזיות_דמוגרפיות\תרחישי_מלל\goal_num_for_gov</t>
-  </si>
-  <si>
-    <t>gov_goals_2030_iplan</t>
-  </si>
-  <si>
-    <t>gov_goals_2035_iplan</t>
-  </si>
-  <si>
-    <t>gov_goals_2040_iplan</t>
-  </si>
-  <si>
-    <t>gov_goals_2045_iplan</t>
-  </si>
-  <si>
-    <t>gov_goals_2050_iplan</t>
-  </si>
-  <si>
-    <t>W:\Projects\הסעת המונים\01_שלב ה\קבצי עבודה\תחזיות_דמוגרפיות\תחזיות_2050\iplan\change_pop</t>
-  </si>
-  <si>
-    <t>creat_forecast_2050_iplan_230720.ipynb</t>
-  </si>
-  <si>
-    <t>EMP_kibolet</t>
-  </si>
-  <si>
-    <t>FILE-SRV\Jtmt\projections_team\תכניות אסטרטגיות לתחבורה ירושלים\תחזיות 2050\תעסוקה\EMP_KIBOLET.gdb</t>
-  </si>
-  <si>
-    <t>okev_factor</t>
-  </si>
-  <si>
-    <t>work_factor_230719</t>
-  </si>
-  <si>
-    <t>join_forecast_iplan_230711.ipynb</t>
-  </si>
-  <si>
-    <t>W:\Projects\הסעת המונים\01_שלב ה\קבצי עבודה\תחזיות_דמוגרפיות\תחזיות_2050\iplan\join_forecast</t>
-  </si>
-  <si>
-    <t>join_kibolt_2050_Jewish_bau_230712.ipynb</t>
-  </si>
-  <si>
-    <t>W:\Projects\הסעת המונים\01_שלב ה\קבצי עבודה\תחזיות_דמוגרפיות\תחזיות_2050\bau\jew_kibolet\input</t>
-  </si>
-  <si>
-    <t>create_age_distribution_bau_230721.ipynb</t>
-  </si>
-  <si>
-    <t>W:\Projects\הסעת המונים\01_שלב ה\קבצי עבודה\תחזיות_דמוגרפיות\תחזיות_2050\bau\jew_kibolet\output</t>
-  </si>
-  <si>
-    <t>230720_forecast_pop_jewish_2020_2025_bau</t>
-  </si>
-  <si>
-    <t>W:\Projects\הסעת המונים\01_שלב ה\קבצי עבודה\תחזיות_דמוגרפיות\תחזיות_2050\bau\jew_pop</t>
-  </si>
-  <si>
-    <t>230709_join_arab_jew_pop_bau.ipynb</t>
-  </si>
-  <si>
-    <t>230720_forecast_pop_jewish_2025_2030_bau</t>
-  </si>
-  <si>
-    <t>230720_forecast_pop_jewish_2030_2035_bau</t>
-  </si>
-  <si>
-    <t>230720_forecast_pop_jewish_2035_2040_bau</t>
-  </si>
-  <si>
-    <t>230720_forecast_pop_jewish_2040_2045_bau</t>
-  </si>
-  <si>
-    <t>230720_forecast_pop_jewish_2045_2050_bau</t>
-  </si>
-  <si>
-    <t>230720_pop_2025_bau</t>
-  </si>
-  <si>
-    <t>W:\Projects\הסעת המונים\01_שלב ה\קבצי עבודה\תחזיות_דמוגרפיות\תחזיות_2050\bau\join_pop</t>
-  </si>
-  <si>
-    <t>change_pop_to_bau_goals_till_2050_230711.ipynb</t>
-  </si>
-  <si>
-    <t>230720_pop_2030_bau</t>
-  </si>
-  <si>
-    <t>230720_pop_2035_bau</t>
-  </si>
-  <si>
-    <t>230720_pop_2040_bau</t>
-  </si>
-  <si>
-    <t>230720_pop_2045_bau</t>
-  </si>
-  <si>
-    <t>230720_pop_2050_bau</t>
-  </si>
-  <si>
-    <t>gov_goals_2025_BAU</t>
-  </si>
-  <si>
-    <t>gov_goals_2030_BAU</t>
-  </si>
-  <si>
-    <t>gov_goals_2035_BAU</t>
-  </si>
-  <si>
-    <t>gov_goals_2040_BAU</t>
-  </si>
-  <si>
-    <t>gov_goals_2045_BAU</t>
-  </si>
-  <si>
-    <t>gov_goals_2050_BAU</t>
-  </si>
-  <si>
-    <t>W:\Projects\הסעת המונים\01_שלב ה\קבצי עבודה\תחזיות_דמוגרפיות\תחזיות_2050\bau\change_pop</t>
-  </si>
-  <si>
-    <t>creat_forecast_2050_bau_230720.ipynb</t>
-  </si>
-  <si>
-    <t>join_forecast_bau_230711.ipynb</t>
-  </si>
-  <si>
-    <t>W:\Projects\הסעת המונים\01_שלב ה\קבצי עבודה\תחזיות_דמוגרפיות\תחזיות_2050\bau\join_forecast</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="143">
+  <si>
+    <t xml:space="preserve">שם קובץ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מיקום מקורי</t>
+  </si>
+  <si>
+    <t xml:space="preserve">קוד בשימוש</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230628_Jewish_kibolt_some_towns_in_yosh_till_2050</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W:\Projects\הסעת המונים\מטרו\01_שלב ה\קבצי עבודה\תחזיות_דמוגרפיות\תחזיות_2050\מרכיבי_תחזית</t>
+  </si>
+  <si>
+    <t xml:space="preserve">join_kibolt_2050_Jewish_230707.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAZ_V4_230518_Published.shp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W:\Model Versions\4.0\TAZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kibolt_jew_by_some_taz_230628.shp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W:\Projects\הסעת המונים\מטרו\01_שלב ה\קבצי עבודה\תחזיות_דמוגרפיות\תחזיות_2050\מרכיבי_תחזית\SHP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jewish_kibolt_some_by_plan_with_taz_num.shp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">index_for_id_polygons_230717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W:\Projects\הסעת המונים\מטרו\01_שלב ה\קבצי עבודה\תחזיות_דמוגרפיות\תחזיות_2050\jtmt\jew_kibolet\input</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230628_id_polygons_for_index.shp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W:\Projects\הסעת המונים\מטרו\01_שלב ה\קבצי עבודה\תחזיות_דמוגרפיות\תחזיות_2050\התפלגות גילים\backround_files</t>
+  </si>
+  <si>
+    <t xml:space="preserve">create_age_distribution_230719.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230720_kibolt_jew_till_2050</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W:\Projects\הסעת המונים\01_שלב ה\קבצי עבודה\תחזיות_דמוגרפיות\תחזיות_2050\jtmt\jew_kibolet\output </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020_jtmt_forcast_full_230720</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FILE-SRV\Jtmt\projections_team\כללי\פעולות\יצירת_מצב_קיים_למס\output</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W:\Projects\הסעת המונים\01_שלב ה\קבצי עבודה\תחזיות_דמוגרפיות\תחזיות_2050\jtmt\jew_kibolet\output</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cost_diversity_for_age_distribution.shp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W:\Data\Forecast\creat_age_distribution\v_1\backround_files\shp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230720_forecast_pop_jewish_2020_2025_jtmt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W:\Projects\הסעת המונים\01_שלב ה\קבצי עבודה\תחזיות_דמוגרפיות\תחזיות_2050\jtmt\jew_pop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230709_join_arab_jew_pop.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230720_forecast_pop_jewish_2025_2030_jtmt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230720_forecast_pop_jewish_2030_2035_jtmt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230720_forecast_pop_jewish_2035_2040_jtmt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230720_forecast_pop_jewish_2040_2045_jtmt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230720_forecast_pop_jewish_2045_2050_jtmt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">taz_Arab_Palestinian_2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W:\Projects\הסעת המונים\01_שלב ה\קבצי עבודה\תחזיות_דמוגרפיות\תחזיות_2050\jtmt\arab_pop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">taz_Arab_Palestinian_2030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">taz_Arab_Palestinian_2035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">taz_Arab_Palestinian_2040</t>
+  </si>
+  <si>
+    <t xml:space="preserve">taz_Arab_Palestinian_2045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">taz_Arab_Palestinian_2050</t>
+  </si>
+  <si>
+    <t xml:space="preserve">join_forecast.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230720_forecast_2025_full</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W:\Projects\הסעת המונים\01_שלב ה\קבצי עבודה\תחזיות_דמוגרפיות\תחזיות_2050\jtmt\join_forecast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230720_forecast_2030_full</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230720_forecast_2035_full</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230720_forecast_2040_full</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230720_forecast_2045_full</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230720_forecast_2050_full</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‏PalestiniansResults_forecast_zone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FILE-SRV\Jtmt\projections_team\תכניות אסטרטגיות לתחבורה ירושלים\תחזיות 2050\עבודת דמוגרף\קבלת מידע\תחזיות_פלסטינים_ערבים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">palestinian_from_demo_230622.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">proj_zones_pls.shp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K:\projections_team\תכניות אסטרטגיות לתחבורה ירושלים\תחזיות 2050\עבודת דמוגרף\קבלת מידע\אזורי_תחזיות_פלסטינים\SHP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAZ_V4_221212_Published.shp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">palestinian_bld_area_pcbs_220710.shp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K:\projections_team\תכניות אסטרטגיות לתחבורה ירושלים\תחזיות 2050\עבודת דמוגרף\פיזור_אוכלוסייה_באזורי_תנועה_פלסטינאים\SHP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ezorey_tnua_600_2015_ITM.SHP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">arab_growth_till_2050_from_demo_230618.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‏ArabTAZ_in_jeru_dis_after_jtmt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230709_arab_growth_vs_kibolt.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kibolet_with_behind_wall_230709.shp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K:\projections_team\תכניות אסטרטגיות לתחבורה ירושלים\תחזיות 2050\קיבולת_ערבי_מחוז_ירושלים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020_jtmt_forcast_full_230710</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hh_size_2050.shp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FILE-SRV\Jtmt\projections_team\תכניות אסטרטגיות לתחבורה ירושלים\תחזיות 2050\קבלת מידע\גודל משק בית\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pre_demo_growth_dislov_2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W:\Projects\הסעת המונים\01_שלב ה\קבצי עבודה\תחזיות_דמוגרפיות\תחזיות_2050\עבודת_דמוגרף\SHP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pre_demo_growth_dislov_2030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pre_demo_growth_dislov_2035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pre_demo_growth_dislov_2040</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pre_demo_growth_dislov_2045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pre_demo_growth_dislov_2050</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W:\Projects\הסעת המונים\01_שלב ה\קבצי עבודה\תחזיות_דמוגרפיות\תחזיות_2050\מרכיבי_תחזית</t>
+  </si>
+  <si>
+    <t xml:space="preserve">join_kibolt_2050_Jewish_iplan_230711.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W:\Projects\הסעת המונים\01_שלב ה\קבצי עבודה\תחזיות_דמוגרפיות\תחזיות_2050\מרכיבי_תחזית\SHP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">index_for_id_polygons_230712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W:\Projects\הסעת המונים\01_שלב ה\קבצי עבודה\תחזיות_דמוגרפיות\תחזיות_2050\iplan\jew_kibolet\input</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230704_taz_num_convert_from_jewish_to_u_orthodox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W:\Projects\הסעת המונים\01_שלב ה\קבצי עבודה\תחזיות_דמוגרפיות\תרחישי_מלל\מרכיבי_תחזית</t>
+  </si>
+  <si>
+    <t xml:space="preserve">forecast_2020_230719_age_dis_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W:\Projects\הסעת המונים\01_שלב ה\קבצי עבודה\תחזיות_דמוגרפיות\תחזיות_2050\התפלגות גילים\backround_files</t>
+  </si>
+  <si>
+    <t xml:space="preserve">create_age_distribution_iplan_230720.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020_jtmt_forcast_full_230719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W:\Projects\הסעת המונים\01_שלב ה\קבצי עבודה\תחזיות_דמוגרפיות\תחזיות_2050\iplan\jew_kibolet\output</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230720_forecast_pop_jewish_2020_2025_iplan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W:\Projects\הסעת המונים\01_שלב ה\קבצי עבודה\תחזיות_דמוגרפיות\תחזיות_2050\iplan\jew_pop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230709_join_arab_jew_pop_iplan.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230720_forecast_pop_jewish_2025_2030_iplan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230720_forecast_pop_jewish_2030_2035_iplan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230720_forecast_pop_jewish_2035_2040_iplan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230720_forecast_pop_jewish_2040_2045_iplan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230720_forecast_pop_jewish_2045_2050_iplan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230720_pop_2025_iplan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W:\Projects\הסעת המונים\01_שלב ה\קבצי עבודה\תחזיות_דמוגרפיות\תחזיות_2050\iplan\join_pop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">change_pop_to_iplan_goals_till_2050_230711.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230720_pop_2030_iplan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230720_pop_2035_iplan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230720_pop_2040_iplan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230720_pop_2045_iplan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230720_pop_2050_iplan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gov_goals_2025_iplan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W:\Projects\הסעת המונים\01_שלב ה\קבצי עבודה\תחזיות_דמוגרפיות\תרחישי_מלל\goal_num_for_gov</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gov_goals_2030_iplan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gov_goals_2035_iplan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gov_goals_2040_iplan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gov_goals_2045_iplan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gov_goals_2050_iplan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W:\Projects\הסעת המונים\01_שלב ה\קבצי עבודה\תחזיות_דמוגרפיות\תחזיות_2050\iplan\change_pop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">creat_forecast_2050_iplan_230720.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMP_kibolet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FILE-SRV\Jtmt\projections_team\תכניות אסטרטגיות לתחבורה ירושלים\תחזיות 2050\תעסוקה\EMP_KIBOLET.gdb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">okev_factor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">work_factor_230719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">join_forecast_iplan_230711.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W:\Projects\הסעת המונים\01_שלב ה\קבצי עבודה\תחזיות_דמוגרפיות\תחזיות_2050\iplan\join_forecast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">join_kibolt_2050_Jewish_bau_230712.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W:\Projects\הסעת המונים\01_שלב ה\קבצי עבודה\תחזיות_דמוגרפיות\תחזיות_2050\bau\jew_kibolet\input</t>
+  </si>
+  <si>
+    <t xml:space="preserve">create_age_distribution_bau_230721.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W:\Projects\הסעת המונים\01_שלב ה\קבצי עבודה\תחזיות_דמוגרפיות\תחזיות_2050\bau\jew_kibolet\output</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230720_forecast_pop_jewish_2020_2025_bau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W:\Projects\הסעת המונים\01_שלב ה\קבצי עבודה\תחזיות_דמוגרפיות\תחזיות_2050\bau\jew_pop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230709_join_arab_jew_pop_bau.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230720_forecast_pop_jewish_2025_2030_bau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230720_forecast_pop_jewish_2030_2035_bau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230720_forecast_pop_jewish_2035_2040_bau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230720_forecast_pop_jewish_2040_2045_bau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230720_forecast_pop_jewish_2045_2050_bau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230720_pop_2025_bau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W:\Projects\הסעת המונים\01_שלב ה\קבצי עבודה\תחזיות_דמוגרפיות\תחזיות_2050\bau\join_pop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">change_pop_to_bau_goals_till_2050_230711.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230720_pop_2030_bau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230720_pop_2035_bau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230720_pop_2040_bau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230720_pop_2045_bau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230720_pop_2050_bau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gov_goals_2025_BAU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gov_goals_2030_BAU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gov_goals_2035_BAU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gov_goals_2040_BAU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gov_goals_2045_BAU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gov_goals_2050_BAU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W:\Projects\הסעת המונים\01_שלב ה\קבצי עבודה\תחזיות_דמוגרפיות\תחזיות_2050\bau\change_pop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">creat_forecast_2050_bau_230720.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">join_forecast_bau_230711.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W:\Projects\הסעת המונים\01_שלב ה\קבצי עבודה\תחזיות_דמוגרפיות\תחזיות_2050\bau\join_forecast</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="General"/>
+  </numFmts>
+  <fonts count="5">
     <font>
-      <sz val="11.0"/>
-      <color theme="1"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
-      <sz val="10.0"/>
-      <color theme="1"/>
+      <sz val="10"/>
       <name val="Arial"/>
+      <family val="0"/>
+      <charset val="177"/>
     </font>
     <font>
-      <sz val="10.0"/>
-      <color theme="1"/>
+      <sz val="10"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
+      <family val="0"/>
+      <charset val="177"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="177"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1280,259 +497,95 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="6">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="center"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="6">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
-  <a:themeElements>
-    <a:clrScheme name="Sheets">
-      <a:dk1>
-        <a:srgbClr val="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="000000"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="FFFFFF"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="ED7D31"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="FFC000"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4472C4"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="70AD47"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0563C1"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="0563C1"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Sheets">
-      <a:majorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <dimension ref="A1:Z1000"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="41.5"/>
-    <col customWidth="1" min="2" max="2" width="93.25"/>
-    <col customWidth="1" min="3" max="3" width="25.88"/>
-    <col customWidth="1" min="4" max="23" width="9.0"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="41.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="93.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="25.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="4" style="0" width="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1">
+    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1566,11 +619,11 @@
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
     </row>
-    <row r="2" ht="14.25" customHeight="1">
+    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -1600,7 +653,7 @@
       <c r="Y2" s="2"/>
       <c r="Z2" s="2"/>
     </row>
-    <row r="3" ht="14.25" customHeight="1">
+    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -1634,11 +687,11 @@
       <c r="Y3" s="2"/>
       <c r="Z3" s="2"/>
     </row>
-    <row r="4" ht="14.25" customHeight="1">
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -1668,12 +721,12 @@
       <c r="Y4" s="2"/>
       <c r="Z4" s="2"/>
     </row>
-    <row r="5" ht="14.25" customHeight="1">
+    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>11</v>
+      <c r="B5" s="3" t="s">
+        <v>9</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>5</v>
@@ -1702,12 +755,12 @@
       <c r="Y5" s="2"/>
       <c r="Z5" s="2"/>
     </row>
-    <row r="6" ht="14.25" customHeight="1">
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>13</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>5</v>
@@ -1736,12 +789,12 @@
       <c r="Y6" s="2"/>
       <c r="Z6" s="2"/>
     </row>
-    <row r="7" ht="14.25" customHeight="1">
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>9</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>5</v>
@@ -1770,13 +823,13 @@
       <c r="Y7" s="2"/>
       <c r="Z7" s="2"/>
     </row>
-    <row r="8" ht="14.25" customHeight="1">
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2"/>
-      <c r="B8" s="4" t="s">
-        <v>16</v>
+      <c r="B8" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -1802,7 +855,7 @@
       <c r="Y8" s="2"/>
       <c r="Z8" s="2"/>
     </row>
-    <row r="9" ht="14.25" customHeight="1">
+    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -1830,12 +883,16 @@
       <c r="Y9" s="2"/>
       <c r="Z9" s="2"/>
     </row>
-    <row r="10" ht="14.25" customHeight="1">
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
+        <v>16</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
@@ -1860,15 +917,15 @@
       <c r="Y10" s="2"/>
       <c r="Z10" s="2"/>
     </row>
-    <row r="11" ht="14.25" customHeight="1">
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="C11" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -1894,15 +951,15 @@
       <c r="Y11" s="2"/>
       <c r="Z11" s="2"/>
     </row>
-    <row r="12" ht="14.25" customHeight="1">
+    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
@@ -1928,15 +985,15 @@
       <c r="Y12" s="2"/>
       <c r="Z12" s="2"/>
     </row>
-    <row r="13" ht="14.25" customHeight="1">
+    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
@@ -1962,7 +1019,7 @@
       <c r="Y13" s="2"/>
       <c r="Z13" s="2"/>
     </row>
-    <row r="14" ht="14.25" customHeight="1">
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -1990,15 +1047,15 @@
       <c r="Y14" s="2"/>
       <c r="Z14" s="2"/>
     </row>
-    <row r="15" ht="14.25" customHeight="1">
+    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
@@ -2024,15 +1081,15 @@
       <c r="Y15" s="2"/>
       <c r="Z15" s="2"/>
     </row>
-    <row r="16" ht="14.25" customHeight="1">
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
@@ -2058,15 +1115,15 @@
       <c r="Y16" s="2"/>
       <c r="Z16" s="2"/>
     </row>
-    <row r="17" ht="14.25" customHeight="1">
+    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
@@ -2092,15 +1149,15 @@
       <c r="Y17" s="2"/>
       <c r="Z17" s="2"/>
     </row>
-    <row r="18" ht="14.25" customHeight="1">
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
@@ -2126,15 +1183,15 @@
       <c r="Y18" s="2"/>
       <c r="Z18" s="2"/>
     </row>
-    <row r="19" ht="14.25" customHeight="1">
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
@@ -2160,15 +1217,15 @@
       <c r="Y19" s="2"/>
       <c r="Z19" s="2"/>
     </row>
-    <row r="20" ht="14.25" customHeight="1">
+    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
@@ -2194,15 +1251,15 @@
       <c r="Y20" s="2"/>
       <c r="Z20" s="2"/>
     </row>
-    <row r="21" ht="14.25" customHeight="1">
+    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
@@ -2228,15 +1285,15 @@
       <c r="Y21" s="2"/>
       <c r="Z21" s="2"/>
     </row>
-    <row r="22" ht="14.25" customHeight="1">
+    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
@@ -2262,15 +1319,15 @@
       <c r="Y22" s="2"/>
       <c r="Z22" s="2"/>
     </row>
-    <row r="23" ht="14.25" customHeight="1">
+    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
@@ -2296,15 +1353,15 @@
       <c r="Y23" s="2"/>
       <c r="Z23" s="2"/>
     </row>
-    <row r="24" ht="14.25" customHeight="1">
+    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
@@ -2330,15 +1387,15 @@
       <c r="Y24" s="2"/>
       <c r="Z24" s="2"/>
     </row>
-    <row r="25" ht="14.25" customHeight="1">
+    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
@@ -2364,15 +1421,15 @@
       <c r="Y25" s="2"/>
       <c r="Z25" s="2"/>
     </row>
-    <row r="26" ht="14.25" customHeight="1">
+    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
@@ -2398,7 +1455,7 @@
       <c r="Y26" s="2"/>
       <c r="Z26" s="2"/>
     </row>
-    <row r="27" ht="14.25" customHeight="1">
+    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -2426,15 +1483,15 @@
       <c r="Y27" s="2"/>
       <c r="Z27" s="2"/>
     </row>
-    <row r="28" ht="14.25" customHeight="1">
+    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="C28" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
@@ -2460,15 +1517,15 @@
       <c r="Y28" s="2"/>
       <c r="Z28" s="2"/>
     </row>
-    <row r="29" ht="14.25" customHeight="1">
+    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
@@ -2494,15 +1551,15 @@
       <c r="Y29" s="2"/>
       <c r="Z29" s="2"/>
     </row>
-    <row r="30" ht="14.25" customHeight="1">
+    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
@@ -2528,15 +1585,15 @@
       <c r="Y30" s="2"/>
       <c r="Z30" s="2"/>
     </row>
-    <row r="31" ht="14.25" customHeight="1">
+    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
@@ -2562,15 +1619,15 @@
       <c r="Y31" s="2"/>
       <c r="Z31" s="2"/>
     </row>
-    <row r="32" ht="14.25" customHeight="1">
+    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
@@ -2596,15 +1653,15 @@
       <c r="Y32" s="2"/>
       <c r="Z32" s="2"/>
     </row>
-    <row r="33" ht="14.25" customHeight="1">
+    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
@@ -2630,15 +1687,15 @@
       <c r="Y33" s="2"/>
       <c r="Z33" s="2"/>
     </row>
-    <row r="34" ht="14.25" customHeight="1">
+    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
@@ -2664,7 +1721,7 @@
       <c r="Y34" s="2"/>
       <c r="Z34" s="2"/>
     </row>
-    <row r="35" ht="14.25" customHeight="1">
+    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -2692,15 +1749,15 @@
       <c r="Y35" s="2"/>
       <c r="Z35" s="2"/>
     </row>
-    <row r="36" ht="14.25" customHeight="1">
+    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
@@ -2726,15 +1783,15 @@
       <c r="Y36" s="2"/>
       <c r="Z36" s="2"/>
     </row>
-    <row r="37" ht="14.25" customHeight="1">
+    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
@@ -2760,15 +1817,15 @@
       <c r="Y37" s="2"/>
       <c r="Z37" s="2"/>
     </row>
-    <row r="38" ht="14.25" customHeight="1">
+    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
@@ -2794,15 +1851,15 @@
       <c r="Y38" s="2"/>
       <c r="Z38" s="2"/>
     </row>
-    <row r="39" ht="14.25" customHeight="1">
+    <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
@@ -2828,7 +1885,7 @@
       <c r="Y39" s="2"/>
       <c r="Z39" s="2"/>
     </row>
-    <row r="40" ht="14.25" customHeight="1">
+    <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -2856,15 +1913,15 @@
       <c r="Y40" s="2"/>
       <c r="Z40" s="2"/>
     </row>
-    <row r="41" ht="14.25" customHeight="1">
+    <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" s="2"/>
@@ -2890,15 +1947,15 @@
       <c r="Y41" s="2"/>
       <c r="Z41" s="2"/>
     </row>
-    <row r="42" ht="14.25" customHeight="1">
+    <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
@@ -2924,7 +1981,7 @@
       <c r="Y42" s="2"/>
       <c r="Z42" s="2"/>
     </row>
-    <row r="43" ht="14.25" customHeight="1">
+    <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -2952,15 +2009,15 @@
       <c r="Y43" s="2"/>
       <c r="Z43" s="2"/>
     </row>
-    <row r="44" ht="14.25" customHeight="1">
+    <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
@@ -2986,15 +2043,15 @@
       <c r="Y44" s="2"/>
       <c r="Z44" s="2"/>
     </row>
-    <row r="45" ht="14.25" customHeight="1">
+    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
@@ -3020,15 +2077,15 @@
       <c r="Y45" s="2"/>
       <c r="Z45" s="2"/>
     </row>
-    <row r="46" ht="14.25" customHeight="1">
+    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
@@ -3054,15 +2111,15 @@
       <c r="Y46" s="2"/>
       <c r="Z46" s="2"/>
     </row>
-    <row r="47" ht="14.25" customHeight="1">
+    <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" s="2"/>
@@ -3088,15 +2145,15 @@
       <c r="Y47" s="2"/>
       <c r="Z47" s="2"/>
     </row>
-    <row r="48" ht="14.25" customHeight="1">
+    <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" s="2"/>
@@ -3122,15 +2179,15 @@
       <c r="Y48" s="2"/>
       <c r="Z48" s="2"/>
     </row>
-    <row r="49" ht="14.25" customHeight="1">
+    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" s="2"/>
@@ -3156,15 +2213,15 @@
       <c r="Y49" s="2"/>
       <c r="Z49" s="2"/>
     </row>
-    <row r="50" ht="14.25" customHeight="1">
+    <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" s="2"/>
@@ -3190,15 +2247,15 @@
       <c r="Y50" s="2"/>
       <c r="Z50" s="2"/>
     </row>
-    <row r="51" ht="14.25" customHeight="1">
+    <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" s="2"/>
@@ -3224,15 +2281,15 @@
       <c r="Y51" s="2"/>
       <c r="Z51" s="2"/>
     </row>
-    <row r="52" ht="14.25" customHeight="1">
+    <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="5" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" s="2"/>
@@ -3258,15 +2315,15 @@
       <c r="Y52" s="2"/>
       <c r="Z52" s="2"/>
     </row>
-    <row r="53" ht="14.25" customHeight="1">
+    <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="5" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" s="2"/>
@@ -3292,7 +2349,7 @@
       <c r="Y53" s="2"/>
       <c r="Z53" s="2"/>
     </row>
-    <row r="54" ht="14.25" customHeight="1">
+    <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -3320,15 +2377,15 @@
       <c r="Y54" s="2"/>
       <c r="Z54" s="2"/>
     </row>
-    <row r="55" ht="14.25" customHeight="1">
+    <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" s="2"/>
@@ -3354,15 +2411,15 @@
       <c r="Y55" s="2"/>
       <c r="Z55" s="2"/>
     </row>
-    <row r="56" ht="14.25" customHeight="1">
+    <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" s="2"/>
@@ -3388,15 +2445,15 @@
       <c r="Y56" s="2"/>
       <c r="Z56" s="2"/>
     </row>
-    <row r="57" ht="14.25" customHeight="1">
+    <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" s="2"/>
@@ -3422,15 +2479,15 @@
       <c r="Y57" s="2"/>
       <c r="Z57" s="2"/>
     </row>
-    <row r="58" ht="14.25" customHeight="1">
+    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
@@ -3456,15 +2513,15 @@
       <c r="Y58" s="2"/>
       <c r="Z58" s="2"/>
     </row>
-    <row r="59" ht="14.25" customHeight="1">
+    <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D59" s="2"/>
       <c r="E59" s="2"/>
@@ -3490,15 +2547,15 @@
       <c r="Y59" s="2"/>
       <c r="Z59" s="2"/>
     </row>
-    <row r="60" ht="14.25" customHeight="1">
+    <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" s="2"/>
@@ -3524,7 +2581,7 @@
       <c r="Y60" s="2"/>
       <c r="Z60" s="2"/>
     </row>
-    <row r="61" ht="14.25" customHeight="1">
+    <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -3552,15 +2609,15 @@
       <c r="Y61" s="2"/>
       <c r="Z61" s="2"/>
     </row>
-    <row r="62" ht="14.25" customHeight="1">
+    <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" s="2"/>
@@ -3586,15 +2643,15 @@
       <c r="Y62" s="2"/>
       <c r="Z62" s="2"/>
     </row>
-    <row r="63" ht="14.25" customHeight="1">
+    <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" s="2"/>
@@ -3620,15 +2677,15 @@
       <c r="Y63" s="2"/>
       <c r="Z63" s="2"/>
     </row>
-    <row r="64" ht="14.25" customHeight="1">
+    <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" s="2"/>
@@ -3654,15 +2711,15 @@
       <c r="Y64" s="2"/>
       <c r="Z64" s="2"/>
     </row>
-    <row r="65" ht="14.25" customHeight="1">
+    <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" s="2"/>
@@ -3688,15 +2745,15 @@
       <c r="Y65" s="2"/>
       <c r="Z65" s="2"/>
     </row>
-    <row r="66" ht="14.25" customHeight="1">
+    <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B66" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C66" s="2" t="s">
         <v>79</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>82</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" s="2"/>
@@ -3722,7 +2779,7 @@
       <c r="Y66" s="2"/>
       <c r="Z66" s="2"/>
     </row>
-    <row r="67" ht="14.25" customHeight="1">
+    <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -3750,15 +2807,15 @@
       <c r="Y67" s="2"/>
       <c r="Z67" s="2"/>
     </row>
-    <row r="68" ht="14.25" customHeight="1">
+    <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D68" s="2"/>
       <c r="E68" s="2"/>
@@ -3784,15 +2841,15 @@
       <c r="Y68" s="2"/>
       <c r="Z68" s="2"/>
     </row>
-    <row r="69" ht="14.25" customHeight="1">
+    <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D69" s="2"/>
       <c r="E69" s="2"/>
@@ -3818,15 +2875,15 @@
       <c r="Y69" s="2"/>
       <c r="Z69" s="2"/>
     </row>
-    <row r="70" ht="14.25" customHeight="1">
+    <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D70" s="2"/>
       <c r="E70" s="2"/>
@@ -3852,15 +2909,15 @@
       <c r="Y70" s="2"/>
       <c r="Z70" s="2"/>
     </row>
-    <row r="71" ht="14.25" customHeight="1">
+    <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" s="2"/>
@@ -3886,15 +2943,15 @@
       <c r="Y71" s="2"/>
       <c r="Z71" s="2"/>
     </row>
-    <row r="72" ht="14.25" customHeight="1">
+    <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" s="2"/>
@@ -3920,15 +2977,15 @@
       <c r="Y72" s="2"/>
       <c r="Z72" s="2"/>
     </row>
-    <row r="73" ht="14.25" customHeight="1">
+    <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D73" s="2"/>
       <c r="E73" s="2"/>
@@ -3954,15 +3011,15 @@
       <c r="Y73" s="2"/>
       <c r="Z73" s="2"/>
     </row>
-    <row r="74" ht="14.25" customHeight="1">
+    <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" s="2"/>
@@ -3988,15 +3045,15 @@
       <c r="Y74" s="2"/>
       <c r="Z74" s="2"/>
     </row>
-    <row r="75" ht="14.25" customHeight="1">
+    <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" s="2"/>
@@ -4022,15 +3079,15 @@
       <c r="Y75" s="2"/>
       <c r="Z75" s="2"/>
     </row>
-    <row r="76" ht="14.25" customHeight="1">
+    <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" s="2"/>
@@ -4056,15 +3113,15 @@
       <c r="Y76" s="2"/>
       <c r="Z76" s="2"/>
     </row>
-    <row r="77" ht="14.25" customHeight="1">
+    <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" s="2"/>
@@ -4090,15 +3147,15 @@
       <c r="Y77" s="2"/>
       <c r="Z77" s="2"/>
     </row>
-    <row r="78" ht="14.25" customHeight="1">
+    <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" s="2"/>
@@ -4124,15 +3181,15 @@
       <c r="Y78" s="2"/>
       <c r="Z78" s="2"/>
     </row>
-    <row r="79" ht="14.25" customHeight="1">
+    <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" s="2"/>
@@ -4158,7 +3215,7 @@
       <c r="Y79" s="2"/>
       <c r="Z79" s="2"/>
     </row>
-    <row r="80" ht="14.25" customHeight="1">
+    <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -4186,15 +3243,15 @@
       <c r="Y80" s="2"/>
       <c r="Z80" s="2"/>
     </row>
-    <row r="81" ht="14.25" customHeight="1">
+    <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" s="2"/>
@@ -4220,15 +3277,15 @@
       <c r="Y81" s="2"/>
       <c r="Z81" s="2"/>
     </row>
-    <row r="82" ht="14.25" customHeight="1">
+    <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" s="2"/>
@@ -4254,15 +3311,15 @@
       <c r="Y82" s="2"/>
       <c r="Z82" s="2"/>
     </row>
-    <row r="83" ht="14.25" customHeight="1">
+    <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D83" s="2"/>
       <c r="E83" s="2"/>
@@ -4288,15 +3345,15 @@
       <c r="Y83" s="2"/>
       <c r="Z83" s="2"/>
     </row>
-    <row r="84" ht="14.25" customHeight="1">
+    <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D84" s="2"/>
       <c r="E84" s="2"/>
@@ -4322,15 +3379,15 @@
       <c r="Y84" s="2"/>
       <c r="Z84" s="2"/>
     </row>
-    <row r="85" ht="14.25" customHeight="1">
+    <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D85" s="2"/>
       <c r="E85" s="2"/>
@@ -4356,15 +3413,15 @@
       <c r="Y85" s="2"/>
       <c r="Z85" s="2"/>
     </row>
-    <row r="86" ht="14.25" customHeight="1">
+    <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D86" s="2"/>
       <c r="E86" s="2"/>
@@ -4390,15 +3447,15 @@
       <c r="Y86" s="2"/>
       <c r="Z86" s="2"/>
     </row>
-    <row r="87" ht="14.25" customHeight="1">
+    <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D87" s="2"/>
       <c r="E87" s="2"/>
@@ -4424,15 +3481,15 @@
       <c r="Y87" s="2"/>
       <c r="Z87" s="2"/>
     </row>
-    <row r="88" ht="14.25" customHeight="1">
+    <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D88" s="2"/>
       <c r="E88" s="2"/>
@@ -4458,15 +3515,15 @@
       <c r="Y88" s="2"/>
       <c r="Z88" s="2"/>
     </row>
-    <row r="89" ht="14.25" customHeight="1">
+    <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D89" s="2"/>
       <c r="E89" s="2"/>
@@ -4492,15 +3549,15 @@
       <c r="Y89" s="2"/>
       <c r="Z89" s="2"/>
     </row>
-    <row r="90" ht="14.25" customHeight="1">
+    <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D90" s="2"/>
       <c r="E90" s="2"/>
@@ -4526,15 +3583,15 @@
       <c r="Y90" s="2"/>
       <c r="Z90" s="2"/>
     </row>
-    <row r="91" ht="14.25" customHeight="1">
+    <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D91" s="2"/>
       <c r="E91" s="2"/>
@@ -4560,15 +3617,15 @@
       <c r="Y91" s="2"/>
       <c r="Z91" s="2"/>
     </row>
-    <row r="92" ht="14.25" customHeight="1">
+    <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D92" s="2"/>
       <c r="E92" s="2"/>
@@ -4594,15 +3651,15 @@
       <c r="Y92" s="2"/>
       <c r="Z92" s="2"/>
     </row>
-    <row r="93" ht="14.25" customHeight="1">
+    <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D93" s="2"/>
       <c r="E93" s="2"/>
@@ -4628,7 +3685,7 @@
       <c r="Y93" s="2"/>
       <c r="Z93" s="2"/>
     </row>
-    <row r="94" ht="14.25" customHeight="1">
+    <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
@@ -4656,15 +3713,15 @@
       <c r="Y94" s="2"/>
       <c r="Z94" s="2"/>
     </row>
-    <row r="95" ht="14.25" customHeight="1">
+    <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D95" s="2"/>
       <c r="E95" s="2"/>
@@ -4690,15 +3747,15 @@
       <c r="Y95" s="2"/>
       <c r="Z95" s="2"/>
     </row>
-    <row r="96" ht="14.25" customHeight="1">
+    <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D96" s="2"/>
       <c r="E96" s="2"/>
@@ -4724,15 +3781,15 @@
       <c r="Y96" s="2"/>
       <c r="Z96" s="2"/>
     </row>
-    <row r="97" ht="14.25" customHeight="1">
+    <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D97" s="2"/>
       <c r="E97" s="2"/>
@@ -4758,15 +3815,15 @@
       <c r="Y97" s="2"/>
       <c r="Z97" s="2"/>
     </row>
-    <row r="98" ht="14.25" customHeight="1">
+    <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D98" s="2"/>
       <c r="E98" s="2"/>
@@ -4792,15 +3849,15 @@
       <c r="Y98" s="2"/>
       <c r="Z98" s="2"/>
     </row>
-    <row r="99" ht="14.25" customHeight="1">
+    <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D99" s="2"/>
       <c r="E99" s="2"/>
@@ -4826,15 +3883,15 @@
       <c r="Y99" s="2"/>
       <c r="Z99" s="2"/>
     </row>
-    <row r="100" ht="14.25" customHeight="1">
+    <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D100" s="2"/>
       <c r="E100" s="2"/>
@@ -4860,15 +3917,15 @@
       <c r="Y100" s="2"/>
       <c r="Z100" s="2"/>
     </row>
-    <row r="101" ht="14.25" customHeight="1">
+    <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B101" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B101" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="C101" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D101" s="2"/>
       <c r="E101" s="2"/>
@@ -4894,15 +3951,15 @@
       <c r="Y101" s="2"/>
       <c r="Z101" s="2"/>
     </row>
-    <row r="102" ht="14.25" customHeight="1">
+    <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D102" s="2"/>
       <c r="E102" s="2"/>
@@ -4928,15 +3985,15 @@
       <c r="Y102" s="2"/>
       <c r="Z102" s="2"/>
     </row>
-    <row r="103" ht="14.25" customHeight="1">
+    <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" s="2"/>
@@ -4962,15 +4019,15 @@
       <c r="Y103" s="2"/>
       <c r="Z103" s="2"/>
     </row>
-    <row r="104" ht="14.25" customHeight="1">
+    <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D104" s="2"/>
       <c r="E104" s="2"/>
@@ -4996,15 +4053,15 @@
       <c r="Y104" s="2"/>
       <c r="Z104" s="2"/>
     </row>
-    <row r="105" ht="14.25" customHeight="1">
+    <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D105" s="2"/>
       <c r="E105" s="2"/>
@@ -5030,7 +4087,7 @@
       <c r="Y105" s="2"/>
       <c r="Z105" s="2"/>
     </row>
-    <row r="106" ht="14.25" customHeight="1">
+    <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
@@ -5058,15 +4115,15 @@
       <c r="Y106" s="2"/>
       <c r="Z106" s="2"/>
     </row>
-    <row r="107" ht="14.25" customHeight="1">
+    <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B107" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B107" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="C107" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D107" s="2"/>
       <c r="E107" s="2"/>
@@ -5092,15 +4149,15 @@
       <c r="Y107" s="2"/>
       <c r="Z107" s="2"/>
     </row>
-    <row r="108" ht="14.25" customHeight="1">
+    <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D108" s="2"/>
       <c r="E108" s="2"/>
@@ -5126,15 +4183,15 @@
       <c r="Y108" s="2"/>
       <c r="Z108" s="2"/>
     </row>
-    <row r="109" ht="14.25" customHeight="1">
+    <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D109" s="2"/>
       <c r="E109" s="2"/>
@@ -5160,15 +4217,15 @@
       <c r="Y109" s="2"/>
       <c r="Z109" s="2"/>
     </row>
-    <row r="110" ht="14.25" customHeight="1">
+    <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D110" s="2"/>
       <c r="E110" s="2"/>
@@ -5194,15 +4251,15 @@
       <c r="Y110" s="2"/>
       <c r="Z110" s="2"/>
     </row>
-    <row r="111" ht="14.25" customHeight="1">
+    <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D111" s="2"/>
       <c r="E111" s="2"/>
@@ -5228,15 +4285,15 @@
       <c r="Y111" s="2"/>
       <c r="Z111" s="2"/>
     </row>
-    <row r="112" ht="14.25" customHeight="1">
+    <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D112" s="2"/>
       <c r="E112" s="2"/>
@@ -5262,15 +4319,15 @@
       <c r="Y112" s="2"/>
       <c r="Z112" s="2"/>
     </row>
-    <row r="113" ht="14.25" customHeight="1">
+    <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D113" s="2"/>
       <c r="E113" s="2"/>
@@ -5296,15 +4353,15 @@
       <c r="Y113" s="2"/>
       <c r="Z113" s="2"/>
     </row>
-    <row r="114" ht="14.25" customHeight="1">
+    <row r="114" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D114" s="2"/>
       <c r="E114" s="2"/>
@@ -5330,7 +4387,7 @@
       <c r="Y114" s="2"/>
       <c r="Z114" s="2"/>
     </row>
-    <row r="115" ht="14.25" customHeight="1">
+    <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
@@ -5358,15 +4415,15 @@
       <c r="Y115" s="2"/>
       <c r="Z115" s="2"/>
     </row>
-    <row r="116" ht="14.25" customHeight="1">
-      <c r="A116" s="6" t="s">
+    <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A116" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B116" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C116" s="6" t="s">
-        <v>116</v>
+      <c r="B116" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="D116" s="2"/>
       <c r="E116" s="2"/>
@@ -5392,15 +4449,15 @@
       <c r="Y116" s="2"/>
       <c r="Z116" s="2"/>
     </row>
-    <row r="117" ht="14.25" customHeight="1">
-      <c r="A117" s="6" t="s">
+    <row r="117" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A117" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B117" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C117" s="6" t="s">
-        <v>116</v>
+      <c r="B117" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="D117" s="2"/>
       <c r="E117" s="2"/>
@@ -5426,15 +4483,15 @@
       <c r="Y117" s="2"/>
       <c r="Z117" s="2"/>
     </row>
-    <row r="118" ht="14.25" customHeight="1">
-      <c r="A118" s="6" t="s">
+    <row r="118" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A118" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B118" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C118" s="6" t="s">
-        <v>116</v>
+      <c r="B118" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="D118" s="2"/>
       <c r="E118" s="2"/>
@@ -5460,15 +4517,15 @@
       <c r="Y118" s="2"/>
       <c r="Z118" s="2"/>
     </row>
-    <row r="119" ht="14.25" customHeight="1">
-      <c r="A119" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="B119" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="C119" s="6" t="s">
-        <v>116</v>
+    <row r="119" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A119" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="D119" s="2"/>
       <c r="E119" s="2"/>
@@ -5494,15 +4551,15 @@
       <c r="Y119" s="2"/>
       <c r="Z119" s="2"/>
     </row>
-    <row r="120" ht="14.25" customHeight="1">
-      <c r="A120" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B120" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C120" s="6" t="s">
-        <v>116</v>
+    <row r="120" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A120" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="D120" s="2"/>
       <c r="E120" s="2"/>
@@ -5528,15 +4585,15 @@
       <c r="Y120" s="2"/>
       <c r="Z120" s="2"/>
     </row>
-    <row r="121" ht="14.25" customHeight="1">
-      <c r="A121" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="B121" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="C121" s="6" t="s">
-        <v>116</v>
+    <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A121" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="D121" s="2"/>
       <c r="E121" s="2"/>
@@ -5562,7 +4619,7 @@
       <c r="Y121" s="2"/>
       <c r="Z121" s="2"/>
     </row>
-    <row r="122" ht="14.25" customHeight="1">
+    <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
@@ -5590,15 +4647,15 @@
       <c r="Y122" s="2"/>
       <c r="Z122" s="2"/>
     </row>
-    <row r="123" ht="14.25" customHeight="1">
-      <c r="A123" s="6" t="s">
+    <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A123" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B123" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B123" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C123" s="6" t="s">
-        <v>118</v>
+      <c r="C123" s="1" t="s">
+        <v>115</v>
       </c>
       <c r="D123" s="2"/>
       <c r="E123" s="2"/>
@@ -5624,15 +4681,15 @@
       <c r="Y123" s="2"/>
       <c r="Z123" s="2"/>
     </row>
-    <row r="124" ht="14.25" customHeight="1">
-      <c r="A124" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B124" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="C124" s="6" t="s">
-        <v>118</v>
+    <row r="124" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A124" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>115</v>
       </c>
       <c r="D124" s="2"/>
       <c r="E124" s="2"/>
@@ -5658,15 +4715,15 @@
       <c r="Y124" s="2"/>
       <c r="Z124" s="2"/>
     </row>
-    <row r="125" ht="14.25" customHeight="1">
-      <c r="A125" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B125" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C125" s="6" t="s">
-        <v>118</v>
+    <row r="125" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A125" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>115</v>
       </c>
       <c r="D125" s="2"/>
       <c r="E125" s="2"/>
@@ -5692,15 +4749,15 @@
       <c r="Y125" s="2"/>
       <c r="Z125" s="2"/>
     </row>
-    <row r="126" ht="14.25" customHeight="1">
-      <c r="A126" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="B126" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="C126" s="6" t="s">
-        <v>118</v>
+    <row r="126" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A126" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>115</v>
       </c>
       <c r="D126" s="2"/>
       <c r="E126" s="2"/>
@@ -5726,7 +4783,7 @@
       <c r="Y126" s="2"/>
       <c r="Z126" s="2"/>
     </row>
-    <row r="127" ht="14.25" customHeight="1">
+    <row r="127" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
@@ -5754,15 +4811,15 @@
       <c r="Y127" s="2"/>
       <c r="Z127" s="2"/>
     </row>
-    <row r="128" ht="14.25" customHeight="1">
-      <c r="A128" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="B128" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="C128" s="6" t="s">
-        <v>122</v>
+    <row r="128" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A128" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>119</v>
       </c>
       <c r="D128" s="2"/>
       <c r="E128" s="2"/>
@@ -5788,15 +4845,15 @@
       <c r="Y128" s="2"/>
       <c r="Z128" s="2"/>
     </row>
-    <row r="129" ht="14.25" customHeight="1">
-      <c r="A129" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="B129" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="C129" s="6" t="s">
-        <v>122</v>
+    <row r="129" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A129" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>119</v>
       </c>
       <c r="D129" s="2"/>
       <c r="E129" s="2"/>
@@ -5822,15 +4879,15 @@
       <c r="Y129" s="2"/>
       <c r="Z129" s="2"/>
     </row>
-    <row r="130" ht="14.25" customHeight="1">
-      <c r="A130" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="B130" s="7" t="s">
+    <row r="130" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A130" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C130" s="6" t="s">
-        <v>122</v>
+      <c r="B130" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>119</v>
       </c>
       <c r="D130" s="2"/>
       <c r="E130" s="2"/>
@@ -5856,15 +4913,15 @@
       <c r="Y130" s="2"/>
       <c r="Z130" s="2"/>
     </row>
-    <row r="131" ht="14.25" customHeight="1">
-      <c r="A131" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="B131" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="C131" s="6" t="s">
+    <row r="131" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A131" s="1" t="s">
         <v>122</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>119</v>
       </c>
       <c r="D131" s="2"/>
       <c r="E131" s="2"/>
@@ -5890,15 +4947,15 @@
       <c r="Y131" s="2"/>
       <c r="Z131" s="2"/>
     </row>
-    <row r="132" ht="14.25" customHeight="1">
-      <c r="A132" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="B132" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="C132" s="6" t="s">
-        <v>122</v>
+    <row r="132" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A132" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>119</v>
       </c>
       <c r="D132" s="2"/>
       <c r="E132" s="2"/>
@@ -5924,15 +4981,15 @@
       <c r="Y132" s="2"/>
       <c r="Z132" s="2"/>
     </row>
-    <row r="133" ht="14.25" customHeight="1">
-      <c r="A133" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="B133" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="C133" s="6" t="s">
-        <v>122</v>
+    <row r="133" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A133" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>119</v>
       </c>
       <c r="D133" s="2"/>
       <c r="E133" s="2"/>
@@ -5958,15 +5015,15 @@
       <c r="Y133" s="2"/>
       <c r="Z133" s="2"/>
     </row>
-    <row r="134" ht="14.25" customHeight="1">
-      <c r="A134" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B134" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C134" s="6" t="s">
-        <v>122</v>
+    <row r="134" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A134" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>119</v>
       </c>
       <c r="D134" s="2"/>
       <c r="E134" s="2"/>
@@ -5992,15 +5049,15 @@
       <c r="Y134" s="2"/>
       <c r="Z134" s="2"/>
     </row>
-    <row r="135" ht="14.25" customHeight="1">
-      <c r="A135" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B135" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C135" s="6" t="s">
-        <v>122</v>
+    <row r="135" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A135" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>119</v>
       </c>
       <c r="D135" s="2"/>
       <c r="E135" s="2"/>
@@ -6026,15 +5083,15 @@
       <c r="Y135" s="2"/>
       <c r="Z135" s="2"/>
     </row>
-    <row r="136" ht="14.25" customHeight="1">
-      <c r="A136" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B136" s="7" t="s">
+    <row r="136" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A136" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C136" s="6" t="s">
-        <v>122</v>
+      <c r="B136" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>119</v>
       </c>
       <c r="D136" s="2"/>
       <c r="E136" s="2"/>
@@ -6060,15 +5117,15 @@
       <c r="Y136" s="2"/>
       <c r="Z136" s="2"/>
     </row>
-    <row r="137" ht="14.25" customHeight="1">
-      <c r="A137" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B137" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C137" s="6" t="s">
-        <v>122</v>
+    <row r="137" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A137" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>119</v>
       </c>
       <c r="D137" s="2"/>
       <c r="E137" s="2"/>
@@ -6094,15 +5151,15 @@
       <c r="Y137" s="2"/>
       <c r="Z137" s="2"/>
     </row>
-    <row r="138" ht="14.25" customHeight="1">
-      <c r="A138" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B138" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C138" s="6" t="s">
-        <v>122</v>
+    <row r="138" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A138" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>119</v>
       </c>
       <c r="D138" s="2"/>
       <c r="E138" s="2"/>
@@ -6128,15 +5185,15 @@
       <c r="Y138" s="2"/>
       <c r="Z138" s="2"/>
     </row>
-    <row r="139" ht="14.25" customHeight="1">
-      <c r="A139" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B139" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C139" s="6" t="s">
-        <v>122</v>
+    <row r="139" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A139" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>119</v>
       </c>
       <c r="D139" s="2"/>
       <c r="E139" s="2"/>
@@ -6162,7 +5219,7 @@
       <c r="Y139" s="2"/>
       <c r="Z139" s="2"/>
     </row>
-    <row r="140" ht="14.25" customHeight="1">
+    <row r="140" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="2"/>
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
@@ -6190,15 +5247,15 @@
       <c r="Y140" s="2"/>
       <c r="Z140" s="2"/>
     </row>
-    <row r="141" ht="14.25" customHeight="1">
-      <c r="A141" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="B141" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="C141" s="6" t="s">
-        <v>130</v>
+    <row r="141" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A141" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="D141" s="2"/>
       <c r="E141" s="2"/>
@@ -6224,15 +5281,15 @@
       <c r="Y141" s="2"/>
       <c r="Z141" s="2"/>
     </row>
-    <row r="142" ht="14.25" customHeight="1">
-      <c r="A142" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="B142" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="C142" s="6" t="s">
-        <v>130</v>
+    <row r="142" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A142" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="D142" s="2"/>
       <c r="E142" s="2"/>
@@ -6258,15 +5315,15 @@
       <c r="Y142" s="2"/>
       <c r="Z142" s="2"/>
     </row>
-    <row r="143" ht="14.25" customHeight="1">
-      <c r="A143" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="B143" s="7" t="s">
+    <row r="143" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A143" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C143" s="6" t="s">
-        <v>130</v>
+      <c r="B143" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="D143" s="2"/>
       <c r="E143" s="2"/>
@@ -6292,15 +5349,15 @@
       <c r="Y143" s="2"/>
       <c r="Z143" s="2"/>
     </row>
-    <row r="144" ht="14.25" customHeight="1">
-      <c r="A144" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="B144" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="C144" s="6" t="s">
+    <row r="144" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A144" s="1" t="s">
         <v>130</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="D144" s="2"/>
       <c r="E144" s="2"/>
@@ -6326,15 +5383,15 @@
       <c r="Y144" s="2"/>
       <c r="Z144" s="2"/>
     </row>
-    <row r="145" ht="14.25" customHeight="1">
-      <c r="A145" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="B145" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="C145" s="6" t="s">
-        <v>130</v>
+    <row r="145" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A145" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="D145" s="2"/>
       <c r="E145" s="2"/>
@@ -6360,15 +5417,15 @@
       <c r="Y145" s="2"/>
       <c r="Z145" s="2"/>
     </row>
-    <row r="146" ht="14.25" customHeight="1">
-      <c r="A146" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="B146" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="C146" s="6" t="s">
-        <v>130</v>
+    <row r="146" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A146" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="D146" s="2"/>
       <c r="E146" s="2"/>
@@ -6394,15 +5451,15 @@
       <c r="Y146" s="2"/>
       <c r="Z146" s="2"/>
     </row>
-    <row r="147" ht="14.25" customHeight="1">
-      <c r="A147" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="B147" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="C147" s="6" t="s">
-        <v>130</v>
+    <row r="147" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A147" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="D147" s="2"/>
       <c r="E147" s="2"/>
@@ -6428,15 +5485,15 @@
       <c r="Y147" s="2"/>
       <c r="Z147" s="2"/>
     </row>
-    <row r="148" ht="14.25" customHeight="1">
-      <c r="A148" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="B148" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="C148" s="6" t="s">
-        <v>130</v>
+    <row r="148" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A148" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="D148" s="2"/>
       <c r="E148" s="2"/>
@@ -6462,15 +5519,15 @@
       <c r="Y148" s="2"/>
       <c r="Z148" s="2"/>
     </row>
-    <row r="149" ht="14.25" customHeight="1">
-      <c r="A149" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="B149" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="C149" s="6" t="s">
-        <v>130</v>
+    <row r="149" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A149" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="D149" s="2"/>
       <c r="E149" s="2"/>
@@ -6496,15 +5553,15 @@
       <c r="Y149" s="2"/>
       <c r="Z149" s="2"/>
     </row>
-    <row r="150" ht="14.25" customHeight="1">
-      <c r="A150" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="B150" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="C150" s="6" t="s">
-        <v>130</v>
+    <row r="150" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A150" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="D150" s="2"/>
       <c r="E150" s="2"/>
@@ -6530,15 +5587,15 @@
       <c r="Y150" s="2"/>
       <c r="Z150" s="2"/>
     </row>
-    <row r="151" ht="14.25" customHeight="1">
-      <c r="A151" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="B151" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="C151" s="6" t="s">
-        <v>130</v>
+    <row r="151" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A151" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="D151" s="2"/>
       <c r="E151" s="2"/>
@@ -6564,15 +5621,15 @@
       <c r="Y151" s="2"/>
       <c r="Z151" s="2"/>
     </row>
-    <row r="152" ht="14.25" customHeight="1">
-      <c r="A152" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="B152" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="C152" s="6" t="s">
-        <v>130</v>
+    <row r="152" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A152" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="D152" s="2"/>
       <c r="E152" s="2"/>
@@ -6598,15 +5655,15 @@
       <c r="Y152" s="2"/>
       <c r="Z152" s="2"/>
     </row>
-    <row r="153" ht="14.25" customHeight="1">
-      <c r="A153" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="B153" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="C153" s="6" t="s">
-        <v>130</v>
+    <row r="153" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A153" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="D153" s="2"/>
       <c r="E153" s="2"/>
@@ -6632,7 +5689,7 @@
       <c r="Y153" s="2"/>
       <c r="Z153" s="2"/>
     </row>
-    <row r="154" ht="14.25" customHeight="1">
+    <row r="154" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
@@ -6660,15 +5717,15 @@
       <c r="Y154" s="2"/>
       <c r="Z154" s="2"/>
     </row>
-    <row r="155" ht="14.25" customHeight="1">
-      <c r="A155" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="B155" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="C155" s="6" t="s">
-        <v>143</v>
+    <row r="155" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A155" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>140</v>
       </c>
       <c r="D155" s="2"/>
       <c r="E155" s="2"/>
@@ -6694,15 +5751,15 @@
       <c r="Y155" s="2"/>
       <c r="Z155" s="2"/>
     </row>
-    <row r="156" ht="14.25" customHeight="1">
-      <c r="A156" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="B156" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="C156" s="6" t="s">
-        <v>143</v>
+    <row r="156" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A156" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>140</v>
       </c>
       <c r="D156" s="2"/>
       <c r="E156" s="2"/>
@@ -6728,15 +5785,15 @@
       <c r="Y156" s="2"/>
       <c r="Z156" s="2"/>
     </row>
-    <row r="157" ht="14.25" customHeight="1">
-      <c r="A157" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="B157" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="C157" s="6" t="s">
-        <v>143</v>
+    <row r="157" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A157" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>140</v>
       </c>
       <c r="D157" s="2"/>
       <c r="E157" s="2"/>
@@ -6762,15 +5819,15 @@
       <c r="Y157" s="2"/>
       <c r="Z157" s="2"/>
     </row>
-    <row r="158" ht="14.25" customHeight="1">
-      <c r="A158" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="B158" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="C158" s="6" t="s">
-        <v>143</v>
+    <row r="158" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A158" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>140</v>
       </c>
       <c r="D158" s="2"/>
       <c r="E158" s="2"/>
@@ -6796,15 +5853,15 @@
       <c r="Y158" s="2"/>
       <c r="Z158" s="2"/>
     </row>
-    <row r="159" ht="14.25" customHeight="1">
-      <c r="A159" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="B159" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="C159" s="6" t="s">
-        <v>143</v>
+    <row r="159" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A159" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>140</v>
       </c>
       <c r="D159" s="2"/>
       <c r="E159" s="2"/>
@@ -6830,15 +5887,15 @@
       <c r="Y159" s="2"/>
       <c r="Z159" s="2"/>
     </row>
-    <row r="160" ht="14.25" customHeight="1">
-      <c r="A160" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="B160" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="C160" s="6" t="s">
-        <v>143</v>
+    <row r="160" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A160" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>140</v>
       </c>
       <c r="D160" s="2"/>
       <c r="E160" s="2"/>
@@ -6864,15 +5921,15 @@
       <c r="Y160" s="2"/>
       <c r="Z160" s="2"/>
     </row>
-    <row r="161" ht="14.25" customHeight="1">
-      <c r="A161" s="6" t="s">
+    <row r="161" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A161" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B161" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B161" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C161" s="6" t="s">
-        <v>143</v>
+      <c r="C161" s="1" t="s">
+        <v>140</v>
       </c>
       <c r="D161" s="2"/>
       <c r="E161" s="2"/>
@@ -6898,15 +5955,15 @@
       <c r="Y161" s="2"/>
       <c r="Z161" s="2"/>
     </row>
-    <row r="162" ht="14.25" customHeight="1">
-      <c r="A162" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="B162" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="C162" s="6" t="s">
-        <v>143</v>
+    <row r="162" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A162" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>140</v>
       </c>
       <c r="D162" s="2"/>
       <c r="E162" s="2"/>
@@ -6932,15 +5989,15 @@
       <c r="Y162" s="2"/>
       <c r="Z162" s="2"/>
     </row>
-    <row r="163" ht="14.25" customHeight="1">
-      <c r="A163" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="B163" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="C163" s="6" t="s">
-        <v>143</v>
+    <row r="163" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A163" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>140</v>
       </c>
       <c r="D163" s="2"/>
       <c r="E163" s="2"/>
@@ -6966,15 +6023,15 @@
       <c r="Y163" s="2"/>
       <c r="Z163" s="2"/>
     </row>
-    <row r="164" ht="14.25" customHeight="1">
-      <c r="A164" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="B164" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C164" s="6" t="s">
-        <v>143</v>
+    <row r="164" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A164" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>140</v>
       </c>
       <c r="D164" s="2"/>
       <c r="E164" s="2"/>
@@ -7000,10 +6057,10 @@
       <c r="Y164" s="2"/>
       <c r="Z164" s="2"/>
     </row>
-    <row r="165" ht="14.25" customHeight="1">
-      <c r="A165" s="6"/>
-      <c r="B165" s="7"/>
-      <c r="C165" s="8"/>
+    <row r="165" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A165" s="1"/>
+      <c r="B165" s="1"/>
+      <c r="C165" s="2"/>
       <c r="D165" s="2"/>
       <c r="E165" s="2"/>
       <c r="F165" s="2"/>
@@ -7028,15 +6085,15 @@
       <c r="Y165" s="2"/>
       <c r="Z165" s="2"/>
     </row>
-    <row r="166" ht="14.25" customHeight="1">
-      <c r="A166" s="6" t="s">
+    <row r="166" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A166" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B166" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B166" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C166" s="6" t="s">
-        <v>144</v>
+      <c r="C166" s="1" t="s">
+        <v>141</v>
       </c>
       <c r="D166" s="2"/>
       <c r="E166" s="2"/>
@@ -7062,15 +6119,15 @@
       <c r="Y166" s="2"/>
       <c r="Z166" s="2"/>
     </row>
-    <row r="167" ht="14.25" customHeight="1">
-      <c r="A167" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B167" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="C167" s="6" t="s">
-        <v>144</v>
+    <row r="167" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A167" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>141</v>
       </c>
       <c r="D167" s="2"/>
       <c r="E167" s="2"/>
@@ -7096,15 +6153,15 @@
       <c r="Y167" s="2"/>
       <c r="Z167" s="2"/>
     </row>
-    <row r="168" ht="14.25" customHeight="1">
-      <c r="A168" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B168" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="C168" s="6" t="s">
-        <v>144</v>
+    <row r="168" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A168" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>141</v>
       </c>
       <c r="D168" s="2"/>
       <c r="E168" s="2"/>
@@ -7130,15 +6187,15 @@
       <c r="Y168" s="2"/>
       <c r="Z168" s="2"/>
     </row>
-    <row r="169" ht="14.25" customHeight="1">
-      <c r="A169" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B169" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="C169" s="6" t="s">
-        <v>144</v>
+    <row r="169" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A169" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>141</v>
       </c>
       <c r="D169" s="2"/>
       <c r="E169" s="2"/>
@@ -7164,15 +6221,15 @@
       <c r="Y169" s="2"/>
       <c r="Z169" s="2"/>
     </row>
-    <row r="170" ht="14.25" customHeight="1">
-      <c r="A170" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B170" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="C170" s="6" t="s">
-        <v>144</v>
+    <row r="170" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A170" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>141</v>
       </c>
       <c r="D170" s="2"/>
       <c r="E170" s="2"/>
@@ -7198,15 +6255,15 @@
       <c r="Y170" s="2"/>
       <c r="Z170" s="2"/>
     </row>
-    <row r="171" ht="14.25" customHeight="1">
-      <c r="A171" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B171" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="C171" s="6" t="s">
-        <v>144</v>
+    <row r="171" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A171" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>141</v>
       </c>
       <c r="D171" s="2"/>
       <c r="E171" s="2"/>
@@ -7232,15 +6289,15 @@
       <c r="Y171" s="2"/>
       <c r="Z171" s="2"/>
     </row>
-    <row r="172" ht="14.25" customHeight="1">
-      <c r="A172" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B172" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="C172" s="6" t="s">
-        <v>144</v>
+    <row r="172" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A172" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>141</v>
       </c>
       <c r="D172" s="2"/>
       <c r="E172" s="2"/>
@@ -7266,14 +6323,14 @@
       <c r="Y172" s="2"/>
       <c r="Z172" s="2"/>
     </row>
-    <row r="173" ht="14.25" customHeight="1">
-      <c r="A173" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="B173" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="C173" s="8"/>
+    <row r="173" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A173" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C173" s="2"/>
       <c r="D173" s="2"/>
       <c r="E173" s="2"/>
       <c r="F173" s="2"/>
@@ -7298,7 +6355,7 @@
       <c r="Y173" s="2"/>
       <c r="Z173" s="2"/>
     </row>
-    <row r="174" ht="14.25" customHeight="1">
+    <row r="174" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
@@ -7326,7 +6383,7 @@
       <c r="Y174" s="2"/>
       <c r="Z174" s="2"/>
     </row>
-    <row r="175" ht="14.25" customHeight="1">
+    <row r="175" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
@@ -7354,7 +6411,7 @@
       <c r="Y175" s="2"/>
       <c r="Z175" s="2"/>
     </row>
-    <row r="176" ht="14.25" customHeight="1">
+    <row r="176" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
@@ -7382,7 +6439,7 @@
       <c r="Y176" s="2"/>
       <c r="Z176" s="2"/>
     </row>
-    <row r="177" ht="14.25" customHeight="1">
+    <row r="177" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
@@ -7410,7 +6467,7 @@
       <c r="Y177" s="2"/>
       <c r="Z177" s="2"/>
     </row>
-    <row r="178" ht="14.25" customHeight="1">
+    <row r="178" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
@@ -7438,7 +6495,7 @@
       <c r="Y178" s="2"/>
       <c r="Z178" s="2"/>
     </row>
-    <row r="179" ht="14.25" customHeight="1">
+    <row r="179" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
@@ -7466,7 +6523,7 @@
       <c r="Y179" s="2"/>
       <c r="Z179" s="2"/>
     </row>
-    <row r="180" ht="14.25" customHeight="1">
+    <row r="180" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="2"/>
@@ -7494,7 +6551,7 @@
       <c r="Y180" s="2"/>
       <c r="Z180" s="2"/>
     </row>
-    <row r="181" ht="14.25" customHeight="1">
+    <row r="181" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="2"/>
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
@@ -7522,7 +6579,7 @@
       <c r="Y181" s="2"/>
       <c r="Z181" s="2"/>
     </row>
-    <row r="182" ht="14.25" customHeight="1">
+    <row r="182" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
@@ -7550,7 +6607,7 @@
       <c r="Y182" s="2"/>
       <c r="Z182" s="2"/>
     </row>
-    <row r="183" ht="14.25" customHeight="1">
+    <row r="183" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="2"/>
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
@@ -7578,7 +6635,7 @@
       <c r="Y183" s="2"/>
       <c r="Z183" s="2"/>
     </row>
-    <row r="184" ht="14.25" customHeight="1">
+    <row r="184" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
@@ -7606,7 +6663,7 @@
       <c r="Y184" s="2"/>
       <c r="Z184" s="2"/>
     </row>
-    <row r="185" ht="14.25" customHeight="1">
+    <row r="185" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="2"/>
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
@@ -7634,7 +6691,7 @@
       <c r="Y185" s="2"/>
       <c r="Z185" s="2"/>
     </row>
-    <row r="186" ht="14.25" customHeight="1">
+    <row r="186" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="2"/>
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
@@ -7662,7 +6719,7 @@
       <c r="Y186" s="2"/>
       <c r="Z186" s="2"/>
     </row>
-    <row r="187" ht="14.25" customHeight="1">
+    <row r="187" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="2"/>
@@ -7690,7 +6747,7 @@
       <c r="Y187" s="2"/>
       <c r="Z187" s="2"/>
     </row>
-    <row r="188" ht="14.25" customHeight="1">
+    <row r="188" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="2"/>
       <c r="B188" s="2"/>
       <c r="C188" s="2"/>
@@ -7718,7 +6775,7 @@
       <c r="Y188" s="2"/>
       <c r="Z188" s="2"/>
     </row>
-    <row r="189" ht="14.25" customHeight="1">
+    <row r="189" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
@@ -7746,7 +6803,7 @@
       <c r="Y189" s="2"/>
       <c r="Z189" s="2"/>
     </row>
-    <row r="190" ht="14.25" customHeight="1">
+    <row r="190" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="2"/>
       <c r="B190" s="2"/>
       <c r="C190" s="2"/>
@@ -7774,7 +6831,7 @@
       <c r="Y190" s="2"/>
       <c r="Z190" s="2"/>
     </row>
-    <row r="191" ht="14.25" customHeight="1">
+    <row r="191" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
@@ -7802,7 +6859,7 @@
       <c r="Y191" s="2"/>
       <c r="Z191" s="2"/>
     </row>
-    <row r="192" ht="14.25" customHeight="1">
+    <row r="192" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
@@ -7830,7 +6887,7 @@
       <c r="Y192" s="2"/>
       <c r="Z192" s="2"/>
     </row>
-    <row r="193" ht="14.25" customHeight="1">
+    <row r="193" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
@@ -7858,7 +6915,7 @@
       <c r="Y193" s="2"/>
       <c r="Z193" s="2"/>
     </row>
-    <row r="194" ht="14.25" customHeight="1">
+    <row r="194" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="2"/>
       <c r="B194" s="2"/>
       <c r="C194" s="2"/>
@@ -7886,7 +6943,7 @@
       <c r="Y194" s="2"/>
       <c r="Z194" s="2"/>
     </row>
-    <row r="195" ht="14.25" customHeight="1">
+    <row r="195" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="2"/>
       <c r="B195" s="2"/>
       <c r="C195" s="2"/>
@@ -7914,7 +6971,7 @@
       <c r="Y195" s="2"/>
       <c r="Z195" s="2"/>
     </row>
-    <row r="196" ht="14.25" customHeight="1">
+    <row r="196" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="2"/>
@@ -7942,7 +6999,7 @@
       <c r="Y196" s="2"/>
       <c r="Z196" s="2"/>
     </row>
-    <row r="197" ht="14.25" customHeight="1">
+    <row r="197" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="2"/>
       <c r="B197" s="2"/>
       <c r="C197" s="2"/>
@@ -7970,7 +7027,7 @@
       <c r="Y197" s="2"/>
       <c r="Z197" s="2"/>
     </row>
-    <row r="198" ht="14.25" customHeight="1">
+    <row r="198" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="2"/>
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
@@ -7998,7 +7055,7 @@
       <c r="Y198" s="2"/>
       <c r="Z198" s="2"/>
     </row>
-    <row r="199" ht="14.25" customHeight="1">
+    <row r="199" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="2"/>
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
@@ -8026,7 +7083,7 @@
       <c r="Y199" s="2"/>
       <c r="Z199" s="2"/>
     </row>
-    <row r="200" ht="14.25" customHeight="1">
+    <row r="200" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
@@ -8054,7 +7111,7 @@
       <c r="Y200" s="2"/>
       <c r="Z200" s="2"/>
     </row>
-    <row r="201" ht="14.25" customHeight="1">
+    <row r="201" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="2"/>
       <c r="B201" s="2"/>
       <c r="C201" s="2"/>
@@ -8082,7 +7139,7 @@
       <c r="Y201" s="2"/>
       <c r="Z201" s="2"/>
     </row>
-    <row r="202" ht="14.25" customHeight="1">
+    <row r="202" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="2"/>
       <c r="B202" s="2"/>
       <c r="C202" s="2"/>
@@ -8110,7 +7167,7 @@
       <c r="Y202" s="2"/>
       <c r="Z202" s="2"/>
     </row>
-    <row r="203" ht="14.25" customHeight="1">
+    <row r="203" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="2"/>
       <c r="B203" s="2"/>
       <c r="C203" s="2"/>
@@ -8138,7 +7195,7 @@
       <c r="Y203" s="2"/>
       <c r="Z203" s="2"/>
     </row>
-    <row r="204" ht="14.25" customHeight="1">
+    <row r="204" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="2"/>
       <c r="B204" s="2"/>
       <c r="C204" s="2"/>
@@ -8166,7 +7223,7 @@
       <c r="Y204" s="2"/>
       <c r="Z204" s="2"/>
     </row>
-    <row r="205" ht="14.25" customHeight="1">
+    <row r="205" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="2"/>
       <c r="B205" s="2"/>
       <c r="C205" s="2"/>
@@ -8194,7 +7251,7 @@
       <c r="Y205" s="2"/>
       <c r="Z205" s="2"/>
     </row>
-    <row r="206" ht="14.25" customHeight="1">
+    <row r="206" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="2"/>
       <c r="B206" s="2"/>
       <c r="C206" s="2"/>
@@ -8222,7 +7279,7 @@
       <c r="Y206" s="2"/>
       <c r="Z206" s="2"/>
     </row>
-    <row r="207" ht="14.25" customHeight="1">
+    <row r="207" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="2"/>
       <c r="B207" s="2"/>
       <c r="C207" s="2"/>
@@ -8250,7 +7307,7 @@
       <c r="Y207" s="2"/>
       <c r="Z207" s="2"/>
     </row>
-    <row r="208" ht="14.25" customHeight="1">
+    <row r="208" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="2"/>
       <c r="B208" s="2"/>
       <c r="C208" s="2"/>
@@ -8278,7 +7335,7 @@
       <c r="Y208" s="2"/>
       <c r="Z208" s="2"/>
     </row>
-    <row r="209" ht="14.25" customHeight="1">
+    <row r="209" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="2"/>
       <c r="B209" s="2"/>
       <c r="C209" s="2"/>
@@ -8306,7 +7363,7 @@
       <c r="Y209" s="2"/>
       <c r="Z209" s="2"/>
     </row>
-    <row r="210" ht="14.25" customHeight="1">
+    <row r="210" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="2"/>
       <c r="B210" s="2"/>
       <c r="C210" s="2"/>
@@ -8334,7 +7391,7 @@
       <c r="Y210" s="2"/>
       <c r="Z210" s="2"/>
     </row>
-    <row r="211" ht="14.25" customHeight="1">
+    <row r="211" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="2"/>
       <c r="B211" s="2"/>
       <c r="C211" s="2"/>
@@ -8362,7 +7419,7 @@
       <c r="Y211" s="2"/>
       <c r="Z211" s="2"/>
     </row>
-    <row r="212" ht="14.25" customHeight="1">
+    <row r="212" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="2"/>
       <c r="B212" s="2"/>
       <c r="C212" s="2"/>
@@ -8390,7 +7447,7 @@
       <c r="Y212" s="2"/>
       <c r="Z212" s="2"/>
     </row>
-    <row r="213" ht="14.25" customHeight="1">
+    <row r="213" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="2"/>
       <c r="B213" s="2"/>
       <c r="C213" s="2"/>
@@ -8418,7 +7475,7 @@
       <c r="Y213" s="2"/>
       <c r="Z213" s="2"/>
     </row>
-    <row r="214" ht="14.25" customHeight="1">
+    <row r="214" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="2"/>
       <c r="B214" s="2"/>
       <c r="C214" s="2"/>
@@ -8446,7 +7503,7 @@
       <c r="Y214" s="2"/>
       <c r="Z214" s="2"/>
     </row>
-    <row r="215" ht="14.25" customHeight="1">
+    <row r="215" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="2"/>
       <c r="B215" s="2"/>
       <c r="C215" s="2"/>
@@ -8474,7 +7531,7 @@
       <c r="Y215" s="2"/>
       <c r="Z215" s="2"/>
     </row>
-    <row r="216" ht="14.25" customHeight="1">
+    <row r="216" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="2"/>
       <c r="B216" s="2"/>
       <c r="C216" s="2"/>
@@ -8502,7 +7559,7 @@
       <c r="Y216" s="2"/>
       <c r="Z216" s="2"/>
     </row>
-    <row r="217" ht="14.25" customHeight="1">
+    <row r="217" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A217" s="2"/>
       <c r="B217" s="2"/>
       <c r="C217" s="2"/>
@@ -8530,7 +7587,7 @@
       <c r="Y217" s="2"/>
       <c r="Z217" s="2"/>
     </row>
-    <row r="218" ht="14.25" customHeight="1">
+    <row r="218" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A218" s="2"/>
       <c r="B218" s="2"/>
       <c r="C218" s="2"/>
@@ -8558,7 +7615,7 @@
       <c r="Y218" s="2"/>
       <c r="Z218" s="2"/>
     </row>
-    <row r="219" ht="14.25" customHeight="1">
+    <row r="219" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="2"/>
       <c r="B219" s="2"/>
       <c r="C219" s="2"/>
@@ -8586,7 +7643,7 @@
       <c r="Y219" s="2"/>
       <c r="Z219" s="2"/>
     </row>
-    <row r="220" ht="14.25" customHeight="1">
+    <row r="220" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A220" s="2"/>
       <c r="B220" s="2"/>
       <c r="C220" s="2"/>
@@ -8614,7 +7671,7 @@
       <c r="Y220" s="2"/>
       <c r="Z220" s="2"/>
     </row>
-    <row r="221" ht="14.25" customHeight="1">
+    <row r="221" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="2"/>
       <c r="B221" s="2"/>
       <c r="C221" s="2"/>
@@ -8642,7 +7699,7 @@
       <c r="Y221" s="2"/>
       <c r="Z221" s="2"/>
     </row>
-    <row r="222" ht="14.25" customHeight="1">
+    <row r="222" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A222" s="2"/>
       <c r="B222" s="2"/>
       <c r="C222" s="2"/>
@@ -8670,7 +7727,7 @@
       <c r="Y222" s="2"/>
       <c r="Z222" s="2"/>
     </row>
-    <row r="223" ht="14.25" customHeight="1">
+    <row r="223" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A223" s="2"/>
       <c r="B223" s="2"/>
       <c r="C223" s="2"/>
@@ -8698,7 +7755,7 @@
       <c r="Y223" s="2"/>
       <c r="Z223" s="2"/>
     </row>
-    <row r="224" ht="14.25" customHeight="1">
+    <row r="224" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A224" s="2"/>
       <c r="B224" s="2"/>
       <c r="C224" s="2"/>
@@ -8726,7 +7783,7 @@
       <c r="Y224" s="2"/>
       <c r="Z224" s="2"/>
     </row>
-    <row r="225" ht="14.25" customHeight="1">
+    <row r="225" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A225" s="2"/>
       <c r="B225" s="2"/>
       <c r="C225" s="2"/>
@@ -8754,7 +7811,7 @@
       <c r="Y225" s="2"/>
       <c r="Z225" s="2"/>
     </row>
-    <row r="226" ht="14.25" customHeight="1">
+    <row r="226" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="2"/>
       <c r="B226" s="2"/>
       <c r="C226" s="2"/>
@@ -8782,7 +7839,7 @@
       <c r="Y226" s="2"/>
       <c r="Z226" s="2"/>
     </row>
-    <row r="227" ht="14.25" customHeight="1">
+    <row r="227" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A227" s="2"/>
       <c r="B227" s="2"/>
       <c r="C227" s="2"/>
@@ -8810,7 +7867,7 @@
       <c r="Y227" s="2"/>
       <c r="Z227" s="2"/>
     </row>
-    <row r="228" ht="14.25" customHeight="1">
+    <row r="228" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A228" s="2"/>
       <c r="B228" s="2"/>
       <c r="C228" s="2"/>
@@ -8838,7 +7895,7 @@
       <c r="Y228" s="2"/>
       <c r="Z228" s="2"/>
     </row>
-    <row r="229" ht="14.25" customHeight="1">
+    <row r="229" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A229" s="2"/>
       <c r="B229" s="2"/>
       <c r="C229" s="2"/>
@@ -8866,7 +7923,7 @@
       <c r="Y229" s="2"/>
       <c r="Z229" s="2"/>
     </row>
-    <row r="230" ht="14.25" customHeight="1">
+    <row r="230" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A230" s="2"/>
       <c r="B230" s="2"/>
       <c r="C230" s="2"/>
@@ -8894,7 +7951,7 @@
       <c r="Y230" s="2"/>
       <c r="Z230" s="2"/>
     </row>
-    <row r="231" ht="14.25" customHeight="1">
+    <row r="231" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A231" s="2"/>
       <c r="B231" s="2"/>
       <c r="C231" s="2"/>
@@ -8922,7 +7979,7 @@
       <c r="Y231" s="2"/>
       <c r="Z231" s="2"/>
     </row>
-    <row r="232" ht="14.25" customHeight="1">
+    <row r="232" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A232" s="2"/>
       <c r="B232" s="2"/>
       <c r="C232" s="2"/>
@@ -8950,7 +8007,7 @@
       <c r="Y232" s="2"/>
       <c r="Z232" s="2"/>
     </row>
-    <row r="233" ht="14.25" customHeight="1">
+    <row r="233" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="2"/>
       <c r="B233" s="2"/>
       <c r="C233" s="2"/>
@@ -8978,7 +8035,7 @@
       <c r="Y233" s="2"/>
       <c r="Z233" s="2"/>
     </row>
-    <row r="234" ht="14.25" customHeight="1">
+    <row r="234" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="2"/>
       <c r="B234" s="2"/>
       <c r="C234" s="2"/>
@@ -9006,7 +8063,7 @@
       <c r="Y234" s="2"/>
       <c r="Z234" s="2"/>
     </row>
-    <row r="235" ht="14.25" customHeight="1">
+    <row r="235" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="2"/>
       <c r="B235" s="2"/>
       <c r="C235" s="2"/>
@@ -9034,7 +8091,7 @@
       <c r="Y235" s="2"/>
       <c r="Z235" s="2"/>
     </row>
-    <row r="236" ht="14.25" customHeight="1">
+    <row r="236" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A236" s="2"/>
       <c r="B236" s="2"/>
       <c r="C236" s="2"/>
@@ -9062,7 +8119,7 @@
       <c r="Y236" s="2"/>
       <c r="Z236" s="2"/>
     </row>
-    <row r="237" ht="14.25" customHeight="1">
+    <row r="237" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A237" s="2"/>
       <c r="B237" s="2"/>
       <c r="C237" s="2"/>
@@ -9090,7 +8147,7 @@
       <c r="Y237" s="2"/>
       <c r="Z237" s="2"/>
     </row>
-    <row r="238" ht="14.25" customHeight="1">
+    <row r="238" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A238" s="2"/>
       <c r="B238" s="2"/>
       <c r="C238" s="2"/>
@@ -9118,7 +8175,7 @@
       <c r="Y238" s="2"/>
       <c r="Z238" s="2"/>
     </row>
-    <row r="239" ht="14.25" customHeight="1">
+    <row r="239" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A239" s="2"/>
       <c r="B239" s="2"/>
       <c r="C239" s="2"/>
@@ -9146,7 +8203,7 @@
       <c r="Y239" s="2"/>
       <c r="Z239" s="2"/>
     </row>
-    <row r="240" ht="14.25" customHeight="1">
+    <row r="240" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A240" s="2"/>
       <c r="B240" s="2"/>
       <c r="C240" s="2"/>
@@ -9174,7 +8231,7 @@
       <c r="Y240" s="2"/>
       <c r="Z240" s="2"/>
     </row>
-    <row r="241" ht="14.25" customHeight="1">
+    <row r="241" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A241" s="2"/>
       <c r="B241" s="2"/>
       <c r="C241" s="2"/>
@@ -9202,7 +8259,7 @@
       <c r="Y241" s="2"/>
       <c r="Z241" s="2"/>
     </row>
-    <row r="242" ht="14.25" customHeight="1">
+    <row r="242" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A242" s="2"/>
       <c r="B242" s="2"/>
       <c r="C242" s="2"/>
@@ -9230,7 +8287,7 @@
       <c r="Y242" s="2"/>
       <c r="Z242" s="2"/>
     </row>
-    <row r="243" ht="15.75" customHeight="1">
+    <row r="243" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A243" s="2"/>
       <c r="B243" s="2"/>
       <c r="C243" s="2"/>
@@ -9258,7 +8315,7 @@
       <c r="Y243" s="2"/>
       <c r="Z243" s="2"/>
     </row>
-    <row r="244" ht="15.75" customHeight="1">
+    <row r="244" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A244" s="2"/>
       <c r="B244" s="2"/>
       <c r="C244" s="2"/>
@@ -9286,7 +8343,7 @@
       <c r="Y244" s="2"/>
       <c r="Z244" s="2"/>
     </row>
-    <row r="245" ht="15.75" customHeight="1">
+    <row r="245" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A245" s="2"/>
       <c r="B245" s="2"/>
       <c r="C245" s="2"/>
@@ -9314,7 +8371,7 @@
       <c r="Y245" s="2"/>
       <c r="Z245" s="2"/>
     </row>
-    <row r="246" ht="15.75" customHeight="1">
+    <row r="246" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A246" s="2"/>
       <c r="B246" s="2"/>
       <c r="C246" s="2"/>
@@ -9342,7 +8399,7 @@
       <c r="Y246" s="2"/>
       <c r="Z246" s="2"/>
     </row>
-    <row r="247" ht="15.75" customHeight="1">
+    <row r="247" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A247" s="2"/>
       <c r="B247" s="2"/>
       <c r="C247" s="2"/>
@@ -9370,7 +8427,7 @@
       <c r="Y247" s="2"/>
       <c r="Z247" s="2"/>
     </row>
-    <row r="248" ht="15.75" customHeight="1">
+    <row r="248" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A248" s="2"/>
       <c r="B248" s="2"/>
       <c r="C248" s="2"/>
@@ -9398,7 +8455,7 @@
       <c r="Y248" s="2"/>
       <c r="Z248" s="2"/>
     </row>
-    <row r="249" ht="15.75" customHeight="1">
+    <row r="249" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A249" s="2"/>
       <c r="B249" s="2"/>
       <c r="C249" s="2"/>
@@ -9426,7 +8483,7 @@
       <c r="Y249" s="2"/>
       <c r="Z249" s="2"/>
     </row>
-    <row r="250" ht="15.75" customHeight="1">
+    <row r="250" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A250" s="2"/>
       <c r="B250" s="2"/>
       <c r="C250" s="2"/>
@@ -9454,7 +8511,7 @@
       <c r="Y250" s="2"/>
       <c r="Z250" s="2"/>
     </row>
-    <row r="251" ht="15.75" customHeight="1">
+    <row r="251" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A251" s="2"/>
       <c r="B251" s="2"/>
       <c r="C251" s="2"/>
@@ -9482,7 +8539,7 @@
       <c r="Y251" s="2"/>
       <c r="Z251" s="2"/>
     </row>
-    <row r="252" ht="15.75" customHeight="1">
+    <row r="252" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A252" s="2"/>
       <c r="B252" s="2"/>
       <c r="C252" s="2"/>
@@ -9510,7 +8567,7 @@
       <c r="Y252" s="2"/>
       <c r="Z252" s="2"/>
     </row>
-    <row r="253" ht="15.75" customHeight="1">
+    <row r="253" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A253" s="2"/>
       <c r="B253" s="2"/>
       <c r="C253" s="2"/>
@@ -9538,7 +8595,7 @@
       <c r="Y253" s="2"/>
       <c r="Z253" s="2"/>
     </row>
-    <row r="254" ht="15.75" customHeight="1">
+    <row r="254" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A254" s="2"/>
       <c r="B254" s="2"/>
       <c r="C254" s="2"/>
@@ -9566,7 +8623,7 @@
       <c r="Y254" s="2"/>
       <c r="Z254" s="2"/>
     </row>
-    <row r="255" ht="15.75" customHeight="1">
+    <row r="255" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A255" s="2"/>
       <c r="B255" s="2"/>
       <c r="C255" s="2"/>
@@ -9594,7 +8651,7 @@
       <c r="Y255" s="2"/>
       <c r="Z255" s="2"/>
     </row>
-    <row r="256" ht="15.75" customHeight="1">
+    <row r="256" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A256" s="2"/>
       <c r="B256" s="2"/>
       <c r="C256" s="2"/>
@@ -9622,7 +8679,7 @@
       <c r="Y256" s="2"/>
       <c r="Z256" s="2"/>
     </row>
-    <row r="257" ht="15.75" customHeight="1">
+    <row r="257" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A257" s="2"/>
       <c r="B257" s="2"/>
       <c r="C257" s="2"/>
@@ -9650,7 +8707,7 @@
       <c r="Y257" s="2"/>
       <c r="Z257" s="2"/>
     </row>
-    <row r="258" ht="15.75" customHeight="1">
+    <row r="258" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A258" s="2"/>
       <c r="B258" s="2"/>
       <c r="C258" s="2"/>
@@ -9678,7 +8735,7 @@
       <c r="Y258" s="2"/>
       <c r="Z258" s="2"/>
     </row>
-    <row r="259" ht="15.75" customHeight="1">
+    <row r="259" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A259" s="2"/>
       <c r="B259" s="2"/>
       <c r="C259" s="2"/>
@@ -9706,7 +8763,7 @@
       <c r="Y259" s="2"/>
       <c r="Z259" s="2"/>
     </row>
-    <row r="260" ht="15.75" customHeight="1">
+    <row r="260" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A260" s="2"/>
       <c r="B260" s="2"/>
       <c r="C260" s="2"/>
@@ -9734,7 +8791,7 @@
       <c r="Y260" s="2"/>
       <c r="Z260" s="2"/>
     </row>
-    <row r="261" ht="15.75" customHeight="1">
+    <row r="261" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A261" s="2"/>
       <c r="B261" s="2"/>
       <c r="C261" s="2"/>
@@ -9762,7 +8819,7 @@
       <c r="Y261" s="2"/>
       <c r="Z261" s="2"/>
     </row>
-    <row r="262" ht="15.75" customHeight="1">
+    <row r="262" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A262" s="2"/>
       <c r="B262" s="2"/>
       <c r="C262" s="2"/>
@@ -9790,7 +8847,7 @@
       <c r="Y262" s="2"/>
       <c r="Z262" s="2"/>
     </row>
-    <row r="263" ht="15.75" customHeight="1">
+    <row r="263" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A263" s="2"/>
       <c r="B263" s="2"/>
       <c r="C263" s="2"/>
@@ -9818,7 +8875,7 @@
       <c r="Y263" s="2"/>
       <c r="Z263" s="2"/>
     </row>
-    <row r="264" ht="15.75" customHeight="1">
+    <row r="264" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A264" s="2"/>
       <c r="B264" s="2"/>
       <c r="C264" s="2"/>
@@ -9846,7 +8903,7 @@
       <c r="Y264" s="2"/>
       <c r="Z264" s="2"/>
     </row>
-    <row r="265" ht="15.75" customHeight="1">
+    <row r="265" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A265" s="2"/>
       <c r="B265" s="2"/>
       <c r="C265" s="2"/>
@@ -9874,7 +8931,7 @@
       <c r="Y265" s="2"/>
       <c r="Z265" s="2"/>
     </row>
-    <row r="266" ht="15.75" customHeight="1">
+    <row r="266" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A266" s="2"/>
       <c r="B266" s="2"/>
       <c r="C266" s="2"/>
@@ -9902,7 +8959,7 @@
       <c r="Y266" s="2"/>
       <c r="Z266" s="2"/>
     </row>
-    <row r="267" ht="15.75" customHeight="1">
+    <row r="267" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A267" s="2"/>
       <c r="B267" s="2"/>
       <c r="C267" s="2"/>
@@ -9930,7 +8987,7 @@
       <c r="Y267" s="2"/>
       <c r="Z267" s="2"/>
     </row>
-    <row r="268" ht="15.75" customHeight="1">
+    <row r="268" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A268" s="2"/>
       <c r="B268" s="2"/>
       <c r="C268" s="2"/>
@@ -9958,7 +9015,7 @@
       <c r="Y268" s="2"/>
       <c r="Z268" s="2"/>
     </row>
-    <row r="269" ht="15.75" customHeight="1">
+    <row r="269" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A269" s="2"/>
       <c r="B269" s="2"/>
       <c r="C269" s="2"/>
@@ -9986,7 +9043,7 @@
       <c r="Y269" s="2"/>
       <c r="Z269" s="2"/>
     </row>
-    <row r="270" ht="15.75" customHeight="1">
+    <row r="270" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A270" s="2"/>
       <c r="B270" s="2"/>
       <c r="C270" s="2"/>
@@ -10014,7 +9071,7 @@
       <c r="Y270" s="2"/>
       <c r="Z270" s="2"/>
     </row>
-    <row r="271" ht="15.75" customHeight="1">
+    <row r="271" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A271" s="2"/>
       <c r="B271" s="2"/>
       <c r="C271" s="2"/>
@@ -10042,7 +9099,7 @@
       <c r="Y271" s="2"/>
       <c r="Z271" s="2"/>
     </row>
-    <row r="272" ht="15.75" customHeight="1">
+    <row r="272" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A272" s="2"/>
       <c r="B272" s="2"/>
       <c r="C272" s="2"/>
@@ -10070,7 +9127,7 @@
       <c r="Y272" s="2"/>
       <c r="Z272" s="2"/>
     </row>
-    <row r="273" ht="15.75" customHeight="1">
+    <row r="273" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A273" s="2"/>
       <c r="B273" s="2"/>
       <c r="C273" s="2"/>
@@ -10098,7 +9155,7 @@
       <c r="Y273" s="2"/>
       <c r="Z273" s="2"/>
     </row>
-    <row r="274" ht="15.75" customHeight="1">
+    <row r="274" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A274" s="2"/>
       <c r="B274" s="2"/>
       <c r="C274" s="2"/>
@@ -10126,7 +9183,7 @@
       <c r="Y274" s="2"/>
       <c r="Z274" s="2"/>
     </row>
-    <row r="275" ht="15.75" customHeight="1">
+    <row r="275" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A275" s="2"/>
       <c r="B275" s="2"/>
       <c r="C275" s="2"/>
@@ -10154,7 +9211,7 @@
       <c r="Y275" s="2"/>
       <c r="Z275" s="2"/>
     </row>
-    <row r="276" ht="15.75" customHeight="1">
+    <row r="276" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A276" s="2"/>
       <c r="B276" s="2"/>
       <c r="C276" s="2"/>
@@ -10182,7 +9239,7 @@
       <c r="Y276" s="2"/>
       <c r="Z276" s="2"/>
     </row>
-    <row r="277" ht="15.75" customHeight="1">
+    <row r="277" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A277" s="2"/>
       <c r="B277" s="2"/>
       <c r="C277" s="2"/>
@@ -10210,7 +9267,7 @@
       <c r="Y277" s="2"/>
       <c r="Z277" s="2"/>
     </row>
-    <row r="278" ht="15.75" customHeight="1">
+    <row r="278" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A278" s="2"/>
       <c r="B278" s="2"/>
       <c r="C278" s="2"/>
@@ -10238,7 +9295,7 @@
       <c r="Y278" s="2"/>
       <c r="Z278" s="2"/>
     </row>
-    <row r="279" ht="15.75" customHeight="1">
+    <row r="279" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A279" s="2"/>
       <c r="B279" s="2"/>
       <c r="C279" s="2"/>
@@ -10266,7 +9323,7 @@
       <c r="Y279" s="2"/>
       <c r="Z279" s="2"/>
     </row>
-    <row r="280" ht="15.75" customHeight="1">
+    <row r="280" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A280" s="2"/>
       <c r="B280" s="2"/>
       <c r="C280" s="2"/>
@@ -10294,7 +9351,7 @@
       <c r="Y280" s="2"/>
       <c r="Z280" s="2"/>
     </row>
-    <row r="281" ht="15.75" customHeight="1">
+    <row r="281" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A281" s="2"/>
       <c r="B281" s="2"/>
       <c r="C281" s="2"/>
@@ -10322,7 +9379,7 @@
       <c r="Y281" s="2"/>
       <c r="Z281" s="2"/>
     </row>
-    <row r="282" ht="15.75" customHeight="1">
+    <row r="282" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A282" s="2"/>
       <c r="B282" s="2"/>
       <c r="C282" s="2"/>
@@ -10350,7 +9407,7 @@
       <c r="Y282" s="2"/>
       <c r="Z282" s="2"/>
     </row>
-    <row r="283" ht="15.75" customHeight="1">
+    <row r="283" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A283" s="2"/>
       <c r="B283" s="2"/>
       <c r="C283" s="2"/>
@@ -10378,7 +9435,7 @@
       <c r="Y283" s="2"/>
       <c r="Z283" s="2"/>
     </row>
-    <row r="284" ht="15.75" customHeight="1">
+    <row r="284" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A284" s="2"/>
       <c r="B284" s="2"/>
       <c r="C284" s="2"/>
@@ -10406,7 +9463,7 @@
       <c r="Y284" s="2"/>
       <c r="Z284" s="2"/>
     </row>
-    <row r="285" ht="15.75" customHeight="1">
+    <row r="285" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A285" s="2"/>
       <c r="B285" s="2"/>
       <c r="C285" s="2"/>
@@ -10434,7 +9491,7 @@
       <c r="Y285" s="2"/>
       <c r="Z285" s="2"/>
     </row>
-    <row r="286" ht="15.75" customHeight="1">
+    <row r="286" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A286" s="2"/>
       <c r="B286" s="2"/>
       <c r="C286" s="2"/>
@@ -10462,7 +9519,7 @@
       <c r="Y286" s="2"/>
       <c r="Z286" s="2"/>
     </row>
-    <row r="287" ht="15.75" customHeight="1">
+    <row r="287" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A287" s="2"/>
       <c r="B287" s="2"/>
       <c r="C287" s="2"/>
@@ -10490,7 +9547,7 @@
       <c r="Y287" s="2"/>
       <c r="Z287" s="2"/>
     </row>
-    <row r="288" ht="15.75" customHeight="1">
+    <row r="288" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A288" s="2"/>
       <c r="B288" s="2"/>
       <c r="C288" s="2"/>
@@ -10518,7 +9575,7 @@
       <c r="Y288" s="2"/>
       <c r="Z288" s="2"/>
     </row>
-    <row r="289" ht="15.75" customHeight="1">
+    <row r="289" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A289" s="2"/>
       <c r="B289" s="2"/>
       <c r="C289" s="2"/>
@@ -10546,7 +9603,7 @@
       <c r="Y289" s="2"/>
       <c r="Z289" s="2"/>
     </row>
-    <row r="290" ht="15.75" customHeight="1">
+    <row r="290" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A290" s="2"/>
       <c r="B290" s="2"/>
       <c r="C290" s="2"/>
@@ -10574,7 +9631,7 @@
       <c r="Y290" s="2"/>
       <c r="Z290" s="2"/>
     </row>
-    <row r="291" ht="15.75" customHeight="1">
+    <row r="291" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A291" s="2"/>
       <c r="B291" s="2"/>
       <c r="C291" s="2"/>
@@ -10602,7 +9659,7 @@
       <c r="Y291" s="2"/>
       <c r="Z291" s="2"/>
     </row>
-    <row r="292" ht="15.75" customHeight="1">
+    <row r="292" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A292" s="2"/>
       <c r="B292" s="2"/>
       <c r="C292" s="2"/>
@@ -10630,7 +9687,7 @@
       <c r="Y292" s="2"/>
       <c r="Z292" s="2"/>
     </row>
-    <row r="293" ht="15.75" customHeight="1">
+    <row r="293" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A293" s="2"/>
       <c r="B293" s="2"/>
       <c r="C293" s="2"/>
@@ -10658,717 +9715,720 @@
       <c r="Y293" s="2"/>
       <c r="Z293" s="2"/>
     </row>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
-    <row r="809" ht="15.75" customHeight="1"/>
-    <row r="810" ht="15.75" customHeight="1"/>
-    <row r="811" ht="15.75" customHeight="1"/>
-    <row r="812" ht="15.75" customHeight="1"/>
-    <row r="813" ht="15.75" customHeight="1"/>
-    <row r="814" ht="15.75" customHeight="1"/>
-    <row r="815" ht="15.75" customHeight="1"/>
-    <row r="816" ht="15.75" customHeight="1"/>
-    <row r="817" ht="15.75" customHeight="1"/>
-    <row r="818" ht="15.75" customHeight="1"/>
-    <row r="819" ht="15.75" customHeight="1"/>
-    <row r="820" ht="15.75" customHeight="1"/>
-    <row r="821" ht="15.75" customHeight="1"/>
-    <row r="822" ht="15.75" customHeight="1"/>
-    <row r="823" ht="15.75" customHeight="1"/>
-    <row r="824" ht="15.75" customHeight="1"/>
-    <row r="825" ht="15.75" customHeight="1"/>
-    <row r="826" ht="15.75" customHeight="1"/>
-    <row r="827" ht="15.75" customHeight="1"/>
-    <row r="828" ht="15.75" customHeight="1"/>
-    <row r="829" ht="15.75" customHeight="1"/>
-    <row r="830" ht="15.75" customHeight="1"/>
-    <row r="831" ht="15.75" customHeight="1"/>
-    <row r="832" ht="15.75" customHeight="1"/>
-    <row r="833" ht="15.75" customHeight="1"/>
-    <row r="834" ht="15.75" customHeight="1"/>
-    <row r="835" ht="15.75" customHeight="1"/>
-    <row r="836" ht="15.75" customHeight="1"/>
-    <row r="837" ht="15.75" customHeight="1"/>
-    <row r="838" ht="15.75" customHeight="1"/>
-    <row r="839" ht="15.75" customHeight="1"/>
-    <row r="840" ht="15.75" customHeight="1"/>
-    <row r="841" ht="15.75" customHeight="1"/>
-    <row r="842" ht="15.75" customHeight="1"/>
-    <row r="843" ht="15.75" customHeight="1"/>
-    <row r="844" ht="15.75" customHeight="1"/>
-    <row r="845" ht="15.75" customHeight="1"/>
-    <row r="846" ht="15.75" customHeight="1"/>
-    <row r="847" ht="15.75" customHeight="1"/>
-    <row r="848" ht="15.75" customHeight="1"/>
-    <row r="849" ht="15.75" customHeight="1"/>
-    <row r="850" ht="15.75" customHeight="1"/>
-    <row r="851" ht="15.75" customHeight="1"/>
-    <row r="852" ht="15.75" customHeight="1"/>
-    <row r="853" ht="15.75" customHeight="1"/>
-    <row r="854" ht="15.75" customHeight="1"/>
-    <row r="855" ht="15.75" customHeight="1"/>
-    <row r="856" ht="15.75" customHeight="1"/>
-    <row r="857" ht="15.75" customHeight="1"/>
-    <row r="858" ht="15.75" customHeight="1"/>
-    <row r="859" ht="15.75" customHeight="1"/>
-    <row r="860" ht="15.75" customHeight="1"/>
-    <row r="861" ht="15.75" customHeight="1"/>
-    <row r="862" ht="15.75" customHeight="1"/>
-    <row r="863" ht="15.75" customHeight="1"/>
-    <row r="864" ht="15.75" customHeight="1"/>
-    <row r="865" ht="15.75" customHeight="1"/>
-    <row r="866" ht="15.75" customHeight="1"/>
-    <row r="867" ht="15.75" customHeight="1"/>
-    <row r="868" ht="15.75" customHeight="1"/>
-    <row r="869" ht="15.75" customHeight="1"/>
-    <row r="870" ht="15.75" customHeight="1"/>
-    <row r="871" ht="15.75" customHeight="1"/>
-    <row r="872" ht="15.75" customHeight="1"/>
-    <row r="873" ht="15.75" customHeight="1"/>
-    <row r="874" ht="15.75" customHeight="1"/>
-    <row r="875" ht="15.75" customHeight="1"/>
-    <row r="876" ht="15.75" customHeight="1"/>
-    <row r="877" ht="15.75" customHeight="1"/>
-    <row r="878" ht="15.75" customHeight="1"/>
-    <row r="879" ht="15.75" customHeight="1"/>
-    <row r="880" ht="15.75" customHeight="1"/>
-    <row r="881" ht="15.75" customHeight="1"/>
-    <row r="882" ht="15.75" customHeight="1"/>
-    <row r="883" ht="15.75" customHeight="1"/>
-    <row r="884" ht="15.75" customHeight="1"/>
-    <row r="885" ht="15.75" customHeight="1"/>
-    <row r="886" ht="15.75" customHeight="1"/>
-    <row r="887" ht="15.75" customHeight="1"/>
-    <row r="888" ht="15.75" customHeight="1"/>
-    <row r="889" ht="15.75" customHeight="1"/>
-    <row r="890" ht="15.75" customHeight="1"/>
-    <row r="891" ht="15.75" customHeight="1"/>
-    <row r="892" ht="15.75" customHeight="1"/>
-    <row r="893" ht="15.75" customHeight="1"/>
-    <row r="894" ht="15.75" customHeight="1"/>
-    <row r="895" ht="15.75" customHeight="1"/>
-    <row r="896" ht="15.75" customHeight="1"/>
-    <row r="897" ht="15.75" customHeight="1"/>
-    <row r="898" ht="15.75" customHeight="1"/>
-    <row r="899" ht="15.75" customHeight="1"/>
-    <row r="900" ht="15.75" customHeight="1"/>
-    <row r="901" ht="15.75" customHeight="1"/>
-    <row r="902" ht="15.75" customHeight="1"/>
-    <row r="903" ht="15.75" customHeight="1"/>
-    <row r="904" ht="15.75" customHeight="1"/>
-    <row r="905" ht="15.75" customHeight="1"/>
-    <row r="906" ht="15.75" customHeight="1"/>
-    <row r="907" ht="15.75" customHeight="1"/>
-    <row r="908" ht="15.75" customHeight="1"/>
-    <row r="909" ht="15.75" customHeight="1"/>
-    <row r="910" ht="15.75" customHeight="1"/>
-    <row r="911" ht="15.75" customHeight="1"/>
-    <row r="912" ht="15.75" customHeight="1"/>
-    <row r="913" ht="15.75" customHeight="1"/>
-    <row r="914" ht="15.75" customHeight="1"/>
-    <row r="915" ht="15.75" customHeight="1"/>
-    <row r="916" ht="15.75" customHeight="1"/>
-    <row r="917" ht="15.75" customHeight="1"/>
-    <row r="918" ht="15.75" customHeight="1"/>
-    <row r="919" ht="15.75" customHeight="1"/>
-    <row r="920" ht="15.75" customHeight="1"/>
-    <row r="921" ht="15.75" customHeight="1"/>
-    <row r="922" ht="15.75" customHeight="1"/>
-    <row r="923" ht="15.75" customHeight="1"/>
-    <row r="924" ht="15.75" customHeight="1"/>
-    <row r="925" ht="15.75" customHeight="1"/>
-    <row r="926" ht="15.75" customHeight="1"/>
-    <row r="927" ht="15.75" customHeight="1"/>
-    <row r="928" ht="15.75" customHeight="1"/>
-    <row r="929" ht="15.75" customHeight="1"/>
-    <row r="930" ht="15.75" customHeight="1"/>
-    <row r="931" ht="15.75" customHeight="1"/>
-    <row r="932" ht="15.75" customHeight="1"/>
-    <row r="933" ht="15.75" customHeight="1"/>
-    <row r="934" ht="15.75" customHeight="1"/>
-    <row r="935" ht="15.75" customHeight="1"/>
-    <row r="936" ht="15.75" customHeight="1"/>
-    <row r="937" ht="15.75" customHeight="1"/>
-    <row r="938" ht="15.75" customHeight="1"/>
-    <row r="939" ht="15.75" customHeight="1"/>
-    <row r="940" ht="15.75" customHeight="1"/>
-    <row r="941" ht="15.75" customHeight="1"/>
-    <row r="942" ht="15.75" customHeight="1"/>
-    <row r="943" ht="15.75" customHeight="1"/>
-    <row r="944" ht="15.75" customHeight="1"/>
-    <row r="945" ht="15.75" customHeight="1"/>
-    <row r="946" ht="15.75" customHeight="1"/>
-    <row r="947" ht="15.75" customHeight="1"/>
-    <row r="948" ht="15.75" customHeight="1"/>
-    <row r="949" ht="15.75" customHeight="1"/>
-    <row r="950" ht="15.75" customHeight="1"/>
-    <row r="951" ht="15.75" customHeight="1"/>
-    <row r="952" ht="15.75" customHeight="1"/>
-    <row r="953" ht="15.75" customHeight="1"/>
-    <row r="954" ht="15.75" customHeight="1"/>
-    <row r="955" ht="15.75" customHeight="1"/>
-    <row r="956" ht="15.75" customHeight="1"/>
-    <row r="957" ht="15.75" customHeight="1"/>
-    <row r="958" ht="15.75" customHeight="1"/>
-    <row r="959" ht="15.75" customHeight="1"/>
-    <row r="960" ht="15.75" customHeight="1"/>
-    <row r="961" ht="15.75" customHeight="1"/>
-    <row r="962" ht="15.75" customHeight="1"/>
-    <row r="963" ht="15.75" customHeight="1"/>
-    <row r="964" ht="15.75" customHeight="1"/>
-    <row r="965" ht="15.75" customHeight="1"/>
-    <row r="966" ht="15.75" customHeight="1"/>
-    <row r="967" ht="15.75" customHeight="1"/>
-    <row r="968" ht="15.75" customHeight="1"/>
-    <row r="969" ht="15.75" customHeight="1"/>
-    <row r="970" ht="15.75" customHeight="1"/>
-    <row r="971" ht="15.75" customHeight="1"/>
-    <row r="972" ht="15.75" customHeight="1"/>
-    <row r="973" ht="15.75" customHeight="1"/>
-    <row r="974" ht="15.75" customHeight="1"/>
-    <row r="975" ht="15.75" customHeight="1"/>
-    <row r="976" ht="15.75" customHeight="1"/>
-    <row r="977" ht="15.75" customHeight="1"/>
-    <row r="978" ht="15.75" customHeight="1"/>
-    <row r="979" ht="15.75" customHeight="1"/>
-    <row r="980" ht="15.75" customHeight="1"/>
-    <row r="981" ht="15.75" customHeight="1"/>
-    <row r="982" ht="15.75" customHeight="1"/>
-    <row r="983" ht="15.75" customHeight="1"/>
-    <row r="984" ht="15.75" customHeight="1"/>
-    <row r="985" ht="15.75" customHeight="1"/>
-    <row r="986" ht="15.75" customHeight="1"/>
-    <row r="987" ht="15.75" customHeight="1"/>
-    <row r="988" ht="15.75" customHeight="1"/>
-    <row r="989" ht="15.75" customHeight="1"/>
-    <row r="990" ht="15.75" customHeight="1"/>
-    <row r="991" ht="15.75" customHeight="1"/>
-    <row r="992" ht="15.75" customHeight="1"/>
-    <row r="993" ht="15.75" customHeight="1"/>
-    <row r="994" ht="15.75" customHeight="1"/>
-    <row r="995" ht="15.75" customHeight="1"/>
-    <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
-    <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="294" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="295" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="296" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="297" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="298" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="299" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="300" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="301" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="302" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="303" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="304" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="305" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="306" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="307" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="308" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="309" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="310" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="311" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="312" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="313" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="314" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="315" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="316" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="317" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="318" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="319" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="320" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="321" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="322" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="323" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="324" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="325" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="326" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="327" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="328" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="329" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="330" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="331" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="332" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="333" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="334" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="335" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="336" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="337" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="338" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="339" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="340" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="341" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="342" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="343" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="344" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="345" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="346" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="347" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="348" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="349" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="350" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="351" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="352" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="353" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="354" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="355" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="356" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="357" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="358" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="359" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="360" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="361" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="362" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="363" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="364" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="365" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="366" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="367" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="368" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="369" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="370" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="371" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="372" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="373" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="374" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="375" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="376" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="377" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="378" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="379" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="380" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="381" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="382" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="383" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="384" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="385" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="386" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="387" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="388" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="389" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="390" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="391" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="392" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="393" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="394" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="395" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="396" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="397" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="398" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="399" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="400" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="401" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="402" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="403" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="404" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="405" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="406" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="407" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="408" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="409" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="410" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="411" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="412" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="413" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="414" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="415" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="416" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="417" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="418" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="419" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="420" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="421" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="422" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="423" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="424" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="425" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="426" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="427" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="428" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="429" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="430" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="431" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="432" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="433" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="434" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="435" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="436" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="437" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="438" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="439" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="440" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="441" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="442" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="443" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="444" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="445" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="446" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="447" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="448" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="449" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="450" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="451" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="452" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="453" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="454" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="455" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="456" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="457" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="458" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="459" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="460" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="461" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="462" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="463" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="464" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="465" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="466" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="467" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="468" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="469" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="470" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="471" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="472" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="473" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="474" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="475" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="476" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="477" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="478" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="479" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="480" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="481" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="482" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="483" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="484" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="485" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="486" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="487" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="488" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="489" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="490" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="491" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="492" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="493" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="494" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="495" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="496" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="497" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="498" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="499" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="500" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="501" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="502" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="503" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="504" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="505" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="506" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="507" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="508" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="509" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="510" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="511" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="512" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="513" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="514" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="515" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="516" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="517" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="518" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="519" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="520" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="521" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="522" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="523" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="524" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="525" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="526" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="527" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="528" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="529" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="530" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="531" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="532" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="533" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="534" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="535" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="536" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="537" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="538" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="539" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="540" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="541" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="542" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="543" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="544" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="545" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="546" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="547" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="548" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="549" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="550" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="551" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="552" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="553" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="554" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="555" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="556" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="557" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="558" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="559" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="560" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="561" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="562" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="563" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="564" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="565" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="566" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="567" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="568" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="569" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="570" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="571" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="572" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="573" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="574" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="575" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="576" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="577" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="578" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="579" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="580" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="581" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="582" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="583" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="584" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="585" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="586" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="587" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="588" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="589" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="590" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="591" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="592" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="593" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="594" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="595" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="596" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="597" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="598" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="599" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="600" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="601" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="602" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="603" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="604" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="605" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="606" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="607" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="608" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="609" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="610" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="611" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="612" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="613" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="614" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="615" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="616" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="617" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="618" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="619" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="620" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="621" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="622" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="623" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="624" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="625" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="626" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="627" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="628" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="629" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="630" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="631" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="632" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="633" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="634" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="635" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="636" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="637" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="638" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="639" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="640" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="641" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="642" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="643" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="644" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="645" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="646" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="647" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="648" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="649" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="650" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="651" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="652" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="653" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="654" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="655" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="656" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="657" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="658" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="659" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="660" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="661" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="662" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="663" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="664" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="665" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="666" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="667" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="668" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="669" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="670" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="671" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="672" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="673" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="674" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="675" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="676" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="677" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="678" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="679" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="680" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="681" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="682" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="683" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="684" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="685" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="686" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="687" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="688" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="689" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="690" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="691" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="692" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="693" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="694" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="695" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="696" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="697" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="698" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="699" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="700" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="701" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="702" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="703" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="704" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="705" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="706" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="707" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="708" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="709" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="710" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="711" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="712" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="713" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="714" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="715" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="716" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="717" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="718" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="719" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="720" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="721" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="722" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="723" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="724" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="725" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="726" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="727" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="728" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="729" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="730" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="731" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="732" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="733" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="734" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="735" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="736" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="737" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="738" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="739" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="740" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="741" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="742" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="743" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="744" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="745" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="746" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="747" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="748" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="749" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="750" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="751" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="752" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="753" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="754" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="755" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="756" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="757" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="758" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="759" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="760" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="761" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="762" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="763" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="764" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="765" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="766" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="767" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="768" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="769" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="770" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="771" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="772" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="773" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="774" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="775" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="776" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="777" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="778" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="779" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="780" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="781" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="782" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="783" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="784" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="785" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="786" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="787" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="788" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="789" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="790" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="791" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="792" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="793" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="794" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="795" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="796" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="797" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="798" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="799" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="800" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="801" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="802" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="803" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="804" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="805" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="806" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="807" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="808" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="809" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="810" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="811" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="812" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="813" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="814" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="815" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="816" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="817" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="818" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="819" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="820" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="821" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="822" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="823" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="824" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="825" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="826" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="827" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="828" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="829" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="830" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="831" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="832" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="833" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="834" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="835" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="836" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="837" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="838" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="839" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="840" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="841" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="842" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="843" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="844" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="845" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="846" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="847" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="848" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="849" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="850" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="851" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="852" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="853" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="854" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="855" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="856" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="857" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="858" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="859" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="860" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="861" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="862" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="863" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="864" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="865" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="866" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="867" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="868" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="869" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="870" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="871" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="872" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="873" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="874" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="875" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="876" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="877" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="878" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="879" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="880" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="881" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="882" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="883" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="884" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="885" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="886" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="887" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="888" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="889" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="890" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="891" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="892" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="893" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="894" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="895" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="896" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="897" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="898" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="899" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="900" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="901" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="902" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="903" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="904" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="905" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="906" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="907" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="908" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="909" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="910" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="911" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="912" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="913" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="914" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="915" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="916" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="917" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="918" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="919" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="920" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="921" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="922" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="923" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="924" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="925" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="926" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="927" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="928" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="929" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="930" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="931" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="932" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="933" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="934" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="935" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="936" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="937" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="938" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="939" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="940" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="941" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="942" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="943" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="944" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="945" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="946" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="947" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="948" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="949" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="950" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="951" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="952" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="953" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="954" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="955" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="956" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="957" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="958" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="959" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="960" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="961" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="962" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="963" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="964" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="965" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="966" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="967" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="968" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="969" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="970" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="971" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="972" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="973" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="974" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="975" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="976" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="977" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="978" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="979" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="980" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="981" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="982" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="983" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="984" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="985" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="986" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="987" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="988" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="989" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="990" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="991" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="992" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="993" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="994" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="995" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="996" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="997" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="998" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="999" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1000" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <drawing r:id="rId1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>